--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2284,51 +2284,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135324388</v>
+        <v>96019471</v>
       </c>
       <c r="B17" t="n">
-        <v>83363</v>
+        <v>92283</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1467</v>
+        <v>2063</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Maskaure, Renskötartjärnen, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>617752</v>
+        <v>617488</v>
       </c>
       <c r="R17" t="n">
-        <v>7316113</v>
+        <v>7316243</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,22 +2349,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,44 +2363,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>På barken av en björkstubbe # Betula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96019471</v>
+        <v>135325814</v>
       </c>
       <c r="B18" t="n">
-        <v>92283</v>
+        <v>92320</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2441,17 +2412,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>617488</v>
+        <v>617583</v>
       </c>
       <c r="R18" t="n">
-        <v>7316243</v>
+        <v>7316339</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2475,12 +2446,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2495,44 +2476,48 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135325814</v>
+        <v>135325815</v>
       </c>
       <c r="B19" t="n">
-        <v>92320</v>
+        <v>92027</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2063</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>617583</v>
+        <v>617465</v>
       </c>
       <c r="R19" t="n">
-        <v>7316339</v>
+        <v>7316316</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2577,7 +2562,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2587,7 +2572,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,48 +2603,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135325815</v>
+        <v>96019501</v>
       </c>
       <c r="B20" t="n">
-        <v>92027</v>
+        <v>92333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>4217</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>617465</v>
+        <v>617402</v>
       </c>
       <c r="R20" t="n">
-        <v>7316316</v>
+        <v>7316257</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2683,22 +2668,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,48 +2693,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96019501</v>
+        <v>96019503</v>
       </c>
       <c r="B21" t="n">
-        <v>92333</v>
+        <v>89156</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4217</v>
+        <v>4412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2764,10 +2740,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617402</v>
+        <v>617439</v>
       </c>
       <c r="R21" t="n">
-        <v>7316257</v>
+        <v>7316241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,11 +2776,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2831,48 +2802,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96019503</v>
+        <v>135322930</v>
       </c>
       <c r="B22" t="n">
-        <v>89156</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617439</v>
+        <v>617763</v>
       </c>
       <c r="R22" t="n">
-        <v>7316241</v>
+        <v>7316118</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2896,12 +2867,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2916,19 +2897,23 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135322930</v>
+        <v>135322933</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2963,10 +2948,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617763</v>
+        <v>617745</v>
       </c>
       <c r="R23" t="n">
-        <v>7316118</v>
+        <v>7316136</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2998,7 +2983,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3008,7 +2993,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3039,7 +3024,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135322933</v>
+        <v>135325800</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3070,17 +3055,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617745</v>
+        <v>617692</v>
       </c>
       <c r="R24" t="n">
-        <v>7316136</v>
+        <v>7316206</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3109,7 +3094,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3104,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,12 +3119,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3150,7 +3135,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135325800</v>
+        <v>135325808</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3185,13 +3170,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>617692</v>
+        <v>617658</v>
       </c>
       <c r="R25" t="n">
-        <v>7316206</v>
+        <v>7316334</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3220,7 +3205,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3230,7 +3215,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3261,7 +3246,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135325808</v>
+        <v>135325820</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3296,13 +3281,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>617658</v>
+        <v>617505</v>
       </c>
       <c r="R26" t="n">
-        <v>7316334</v>
+        <v>7316297</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3331,7 +3316,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3341,7 +3326,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3372,32 +3357,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135325820</v>
+        <v>135325824</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>78776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3407,13 +3392,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>617505</v>
+        <v>617617</v>
       </c>
       <c r="R27" t="n">
-        <v>7316297</v>
+        <v>7316184</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3442,7 +3427,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3452,7 +3437,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3483,7 +3468,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135325824</v>
+        <v>135326164</v>
       </c>
       <c r="B28" t="n">
         <v>78776</v>
@@ -3514,14 +3499,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>617617</v>
+        <v>617552</v>
       </c>
       <c r="R28" t="n">
-        <v>7316184</v>
+        <v>7316225</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3553,7 +3538,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3563,7 +3548,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3578,12 +3563,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3594,10 +3579,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135326164</v>
+        <v>135322133</v>
       </c>
       <c r="B29" t="n">
-        <v>78776</v>
+        <v>83358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3605,34 +3590,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>617552</v>
+        <v>617704</v>
       </c>
       <c r="R29" t="n">
-        <v>7316225</v>
+        <v>7316223</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3664,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3674,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3689,12 +3674,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3705,7 +3690,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135322133</v>
+        <v>135322927</v>
       </c>
       <c r="B30" t="n">
         <v>83358</v>
@@ -3736,14 +3721,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617704</v>
+        <v>617778</v>
       </c>
       <c r="R30" t="n">
-        <v>7316223</v>
+        <v>7316112</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3775,7 +3760,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3785,7 +3770,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3800,12 +3785,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3816,7 +3801,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135322927</v>
+        <v>135322940</v>
       </c>
       <c r="B31" t="n">
         <v>83358</v>
@@ -3851,13 +3836,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617778</v>
+        <v>617520</v>
       </c>
       <c r="R31" t="n">
-        <v>7316112</v>
+        <v>7316320</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3886,7 +3871,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3896,7 +3881,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3927,7 +3912,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135322940</v>
+        <v>135325798</v>
       </c>
       <c r="B32" t="n">
         <v>83358</v>
@@ -3958,17 +3943,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>617520</v>
+        <v>617722</v>
       </c>
       <c r="R32" t="n">
-        <v>7316320</v>
+        <v>7316104</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3997,7 +3982,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4007,7 +3992,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4022,12 +4007,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4038,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135325798</v>
+        <v>135325799</v>
       </c>
       <c r="B33" t="n">
         <v>83358</v>
@@ -4073,13 +4058,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>617722</v>
+        <v>617701</v>
       </c>
       <c r="R33" t="n">
-        <v>7316104</v>
+        <v>7316164</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4108,7 +4093,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4118,7 +4103,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4149,7 +4134,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135325799</v>
+        <v>135325801</v>
       </c>
       <c r="B34" t="n">
         <v>83358</v>
@@ -4184,13 +4169,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>617701</v>
+        <v>617709</v>
       </c>
       <c r="R34" t="n">
-        <v>7316164</v>
+        <v>7316204</v>
       </c>
       <c r="S34" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4219,7 +4204,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4229,7 +4214,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4260,7 +4245,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135325801</v>
+        <v>135325805</v>
       </c>
       <c r="B35" t="n">
         <v>83358</v>
@@ -4295,13 +4280,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617709</v>
+        <v>617678</v>
       </c>
       <c r="R35" t="n">
-        <v>7316204</v>
+        <v>7316280</v>
       </c>
       <c r="S35" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4330,7 +4315,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4340,7 +4325,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4371,7 +4356,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135325805</v>
+        <v>135325813</v>
       </c>
       <c r="B36" t="n">
         <v>83358</v>
@@ -4406,13 +4391,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617678</v>
+        <v>617583</v>
       </c>
       <c r="R36" t="n">
-        <v>7316280</v>
+        <v>7316339</v>
       </c>
       <c r="S36" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4441,7 +4426,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4451,7 +4436,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4482,10 +4467,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135325813</v>
+        <v>135322137</v>
       </c>
       <c r="B37" t="n">
-        <v>83358</v>
+        <v>79992</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4493,37 +4478,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>617583</v>
+        <v>617622</v>
       </c>
       <c r="R37" t="n">
-        <v>7316339</v>
+        <v>7316280</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4552,7 +4537,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4562,7 +4547,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4577,12 +4562,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4593,7 +4578,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135322137</v>
+        <v>135322138</v>
       </c>
       <c r="B38" t="n">
         <v>79992</v>
@@ -4628,10 +4613,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>617622</v>
+        <v>617729</v>
       </c>
       <c r="R38" t="n">
-        <v>7316280</v>
+        <v>7316047</v>
       </c>
       <c r="S38" t="n">
         <v>6</v>
@@ -4663,7 +4648,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4673,7 +4658,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4704,7 +4689,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135322138</v>
+        <v>135322139</v>
       </c>
       <c r="B39" t="n">
         <v>79992</v>
@@ -4739,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617729</v>
+        <v>617634</v>
       </c>
       <c r="R39" t="n">
-        <v>7316047</v>
+        <v>7316176</v>
       </c>
       <c r="S39" t="n">
         <v>6</v>
@@ -4815,7 +4800,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135322139</v>
+        <v>135322945</v>
       </c>
       <c r="B40" t="n">
         <v>79992</v>
@@ -4846,17 +4831,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617634</v>
+        <v>617566</v>
       </c>
       <c r="R40" t="n">
-        <v>7316176</v>
+        <v>7316256</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4885,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4895,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4910,12 +4895,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4926,7 +4911,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135322945</v>
+        <v>135325797</v>
       </c>
       <c r="B41" t="n">
         <v>79992</v>
@@ -4957,17 +4942,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>617566</v>
+        <v>617722</v>
       </c>
       <c r="R41" t="n">
-        <v>7316256</v>
+        <v>7316104</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4996,7 +4981,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5006,7 +4991,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5021,12 +5006,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5037,7 +5022,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135324400</v>
+        <v>135325811</v>
       </c>
       <c r="B42" t="n">
         <v>79992</v>
@@ -5068,14 +5053,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Maskaure, Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>617647</v>
+        <v>617596</v>
       </c>
       <c r="R42" t="n">
-        <v>7316156</v>
+        <v>7316363</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5107,7 +5092,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5117,7 +5102,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5128,38 +5113,27 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Gammal tallrotvälta # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135325797</v>
+        <v>135325821</v>
       </c>
       <c r="B43" t="n">
         <v>79992</v>
@@ -5194,13 +5168,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>617722</v>
+        <v>617586</v>
       </c>
       <c r="R43" t="n">
-        <v>7316104</v>
+        <v>7316239</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5229,7 +5203,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5239,7 +5213,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5270,7 +5244,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135325811</v>
+        <v>135325825</v>
       </c>
       <c r="B44" t="n">
         <v>79992</v>
@@ -5305,10 +5279,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>617596</v>
+        <v>617617</v>
       </c>
       <c r="R44" t="n">
-        <v>7316363</v>
+        <v>7316184</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5340,7 +5314,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5350,7 +5324,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5381,7 +5355,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135325821</v>
+        <v>135326163</v>
       </c>
       <c r="B45" t="n">
         <v>79992</v>
@@ -5412,17 +5386,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>617586</v>
+        <v>617613</v>
       </c>
       <c r="R45" t="n">
-        <v>7316239</v>
+        <v>7316170</v>
       </c>
       <c r="S45" t="n">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5451,7 +5425,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5461,27 +5435,28 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5492,10 +5467,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135325825</v>
+        <v>96019502</v>
       </c>
       <c r="B46" t="n">
-        <v>79992</v>
+        <v>78334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5503,37 +5478,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>617617</v>
+        <v>617477</v>
       </c>
       <c r="R46" t="n">
-        <v>7316184</v>
+        <v>7316220</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5557,22 +5532,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:46</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:46</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5587,26 +5552,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135326163</v>
+        <v>135322941</v>
       </c>
       <c r="B47" t="n">
-        <v>79992</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5614,37 +5575,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>617613</v>
+        <v>617391</v>
       </c>
       <c r="R47" t="n">
-        <v>7316170</v>
+        <v>7316296</v>
       </c>
       <c r="S47" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5673,7 +5639,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5683,28 +5649,27 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5715,10 +5680,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>96019502</v>
+        <v>135326171</v>
       </c>
       <c r="B48" t="n">
-        <v>78334</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5726,37 +5691,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>617477</v>
+        <v>617392</v>
       </c>
       <c r="R48" t="n">
-        <v>7316220</v>
+        <v>7316308</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5780,12 +5753,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5800,50 +5788,58 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135322941</v>
+        <v>135322928</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5852,10 +5848,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>617391</v>
+        <v>617773</v>
       </c>
       <c r="R49" t="n">
-        <v>7316296</v>
+        <v>7316117</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5887,7 +5883,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5897,7 +5893,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5928,56 +5924,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135326171</v>
+        <v>135326169</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>98219</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>219815</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>617392</v>
+        <v>617380</v>
       </c>
       <c r="R50" t="n">
-        <v>7316308</v>
+        <v>7316322</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6006,7 +5994,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6016,12 +6004,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6052,54 +6035,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135322928</v>
+        <v>135322932</v>
       </c>
       <c r="B51" t="n">
-        <v>57162</v>
+        <v>78382</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>228579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>617773</v>
+        <v>617752</v>
       </c>
       <c r="R51" t="n">
-        <v>7316117</v>
+        <v>7316138</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6131,7 +6105,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6141,7 +6115,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6172,45 +6146,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135324389</v>
+        <v>135326166</v>
       </c>
       <c r="B52" t="n">
-        <v>5201</v>
+        <v>78382</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>228579</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Maskaure, Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>617710</v>
+        <v>617505</v>
       </c>
       <c r="R52" t="n">
-        <v>7316168</v>
+        <v>7316325</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6242,7 +6216,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6252,7 +6226,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6263,76 +6237,65 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135324396</v>
+        <v>135326173</v>
       </c>
       <c r="B53" t="n">
-        <v>5201</v>
+        <v>78382</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>228579</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Maskaure, Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>617577</v>
+        <v>617462</v>
       </c>
       <c r="R53" t="n">
-        <v>7316342</v>
+        <v>7316207</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6364,7 +6327,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6374,7 +6337,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6385,41 +6348,30 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Klen granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135324386</v>
+        <v>135322946</v>
       </c>
       <c r="B54" t="n">
-        <v>41606</v>
+        <v>79963</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6427,39 +6379,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>215713</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Maskaure, Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>617763</v>
+        <v>617647</v>
       </c>
       <c r="R54" t="n">
-        <v>7316087</v>
+        <v>7316156</v>
       </c>
       <c r="S54" t="n">
         <v>7</v>
@@ -6491,7 +6438,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6501,7 +6448,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6516,60 +6463,64 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135326169</v>
+        <v>135322948</v>
       </c>
       <c r="B55" t="n">
-        <v>98219</v>
+        <v>79396</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219815</v>
+        <v>260591</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>617380</v>
+        <v>617649</v>
       </c>
       <c r="R55" t="n">
-        <v>7316322</v>
+        <v>7316156</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6598,7 +6549,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6608,7 +6559,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Med gula soral</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6623,12 +6579,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6639,45 +6595,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135324390</v>
+        <v>135326162</v>
       </c>
       <c r="B56" t="n">
-        <v>110023</v>
+        <v>79396</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220263</v>
+        <v>260591</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällskråp</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Petasites frigidus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Maskaure, Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>617694</v>
+        <v>617639</v>
       </c>
       <c r="R56" t="n">
-        <v>7316205</v>
+        <v>7316143</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6709,7 +6665,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6719,7 +6675,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6734,60 +6690,59 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135324394</v>
+        <v>135322935</v>
       </c>
       <c r="B57" t="n">
-        <v>99217</v>
+        <v>80267</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
+        <v>266179</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lecidea subhumida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Vain.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Maskaure, Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>617684</v>
+        <v>617720</v>
       </c>
       <c r="R57" t="n">
-        <v>7316239</v>
+        <v>7316234</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6816,7 +6771,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6826,7 +6781,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6841,44 +6796,43 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135322932</v>
+        <v>135322939</v>
       </c>
       <c r="B58" t="n">
-        <v>78382</v>
+        <v>80267</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
+        <v>266179</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lecidea subhumida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Vain.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6888,13 +6842,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>617752</v>
+        <v>617550</v>
       </c>
       <c r="R58" t="n">
-        <v>7316138</v>
+        <v>7316331</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6923,7 +6877,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6933,7 +6887,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6957,778 +6911,6 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135326166</v>
-      </c>
-      <c r="B59" t="n">
-        <v>78382</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>617505</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7316325</v>
-      </c>
-      <c r="S59" t="n">
-        <v>5</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>135326173</v>
-      </c>
-      <c r="B60" t="n">
-        <v>78382</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>617462</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7316207</v>
-      </c>
-      <c r="S60" t="n">
-        <v>5</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>135322946</v>
-      </c>
-      <c r="B61" t="n">
-        <v>79963</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Maskaure Långmyran, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>617647</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7316156</v>
-      </c>
-      <c r="S61" t="n">
-        <v>7</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>135322948</v>
-      </c>
-      <c r="B62" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Maskaure Långmyran, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>617649</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7316156</v>
-      </c>
-      <c r="S62" t="n">
-        <v>14</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Med gula soral</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>135326162</v>
-      </c>
-      <c r="B63" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>617639</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7316143</v>
-      </c>
-      <c r="S63" t="n">
-        <v>5</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>135322935</v>
-      </c>
-      <c r="B64" t="n">
-        <v>80267</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>266179</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Lecidea subhumida</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Vain.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Maskaure Långmyran, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>617720</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7316234</v>
-      </c>
-      <c r="S64" t="n">
-        <v>6</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>135322939</v>
-      </c>
-      <c r="B65" t="n">
-        <v>80267</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>266179</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Lecidea subhumida</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Vain.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Maskaure Långmyran, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>617550</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7316331</v>
-      </c>
-      <c r="S65" t="n">
-        <v>9</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5355,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135326163</v>
+        <v>96019502</v>
       </c>
       <c r="B45" t="n">
-        <v>79992</v>
+        <v>78334</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,37 +5366,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>617613</v>
+        <v>617477</v>
       </c>
       <c r="R45" t="n">
-        <v>7316170</v>
+        <v>7316220</v>
       </c>
       <c r="S45" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5420,57 +5420,42 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>96019502</v>
+        <v>135322941</v>
       </c>
       <c r="B46" t="n">
-        <v>78334</v>
+        <v>57975</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5478,37 +5463,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>617477</v>
+        <v>617391</v>
       </c>
       <c r="R46" t="n">
-        <v>7316220</v>
+        <v>7316296</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5532,12 +5522,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5552,50 +5552,58 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135322941</v>
+        <v>135322928</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5604,10 +5612,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>617391</v>
+        <v>617773</v>
       </c>
       <c r="R47" t="n">
-        <v>7316296</v>
+        <v>7316117</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5639,7 +5647,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5649,7 +5657,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5680,56 +5688,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135326171</v>
+        <v>135326169</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>98219</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>219815</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>617392</v>
+        <v>617380</v>
       </c>
       <c r="R48" t="n">
-        <v>7316308</v>
+        <v>7316322</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5768,12 +5768,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5804,54 +5799,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135322928</v>
+        <v>135322932</v>
       </c>
       <c r="B49" t="n">
-        <v>57162</v>
+        <v>78382</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>228579</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>617773</v>
+        <v>617752</v>
       </c>
       <c r="R49" t="n">
-        <v>7316117</v>
+        <v>7316138</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5883,7 +5869,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5893,7 +5879,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5924,32 +5910,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135326169</v>
+        <v>135326166</v>
       </c>
       <c r="B50" t="n">
-        <v>98219</v>
+        <v>78382</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219815</v>
+        <v>228579</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5959,13 +5945,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>617380</v>
+        <v>617505</v>
       </c>
       <c r="R50" t="n">
-        <v>7316322</v>
+        <v>7316325</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5994,7 +5980,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6004,7 +5990,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6035,7 +6021,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135322932</v>
+        <v>135326173</v>
       </c>
       <c r="B51" t="n">
         <v>78382</v>
@@ -6066,14 +6052,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>617752</v>
+        <v>617462</v>
       </c>
       <c r="R51" t="n">
-        <v>7316138</v>
+        <v>7316207</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6105,7 +6091,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6115,7 +6101,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6130,12 +6116,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6146,10 +6132,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135326166</v>
+        <v>135322946</v>
       </c>
       <c r="B52" t="n">
-        <v>78382</v>
+        <v>79963</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6157,37 +6143,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228579</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>617505</v>
+        <v>617647</v>
       </c>
       <c r="R52" t="n">
-        <v>7316325</v>
+        <v>7316156</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6216,7 +6202,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6226,7 +6212,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6241,12 +6227,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6257,10 +6243,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135326173</v>
+        <v>135322948</v>
       </c>
       <c r="B53" t="n">
-        <v>78382</v>
+        <v>79396</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6268,37 +6254,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>260591</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>617462</v>
+        <v>617649</v>
       </c>
       <c r="R53" t="n">
-        <v>7316207</v>
+        <v>7316156</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6338,6 +6324,11 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Med gula soral</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6352,12 +6343,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6368,10 +6359,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135322946</v>
+        <v>135326162</v>
       </c>
       <c r="B54" t="n">
-        <v>79963</v>
+        <v>79396</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6379,37 +6370,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>260591</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>617647</v>
+        <v>617639</v>
       </c>
       <c r="R54" t="n">
-        <v>7316156</v>
+        <v>7316143</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6438,7 +6429,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6448,7 +6439,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6463,12 +6454,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6479,32 +6470,27 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135322948</v>
+        <v>135322935</v>
       </c>
       <c r="B55" t="n">
-        <v>79396</v>
+        <v>80267</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
+        <v>266179</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lecidea subhumida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Vain.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6514,13 +6500,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>617649</v>
+        <v>617720</v>
       </c>
       <c r="R55" t="n">
-        <v>7316156</v>
+        <v>7316234</v>
       </c>
       <c r="S55" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6549,7 +6535,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6559,12 +6545,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Med gula soral</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6595,48 +6576,43 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135326162</v>
+        <v>135322939</v>
       </c>
       <c r="B56" t="n">
-        <v>79396</v>
+        <v>80267</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
+        <v>266179</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lecidea subhumida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Vain.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>617639</v>
+        <v>617550</v>
       </c>
       <c r="R56" t="n">
-        <v>7316143</v>
+        <v>7316331</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6665,7 +6641,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6675,7 +6651,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6690,227 +6666,15 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>135322935</v>
-      </c>
-      <c r="B57" t="n">
-        <v>80267</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>266179</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Lecidea subhumida</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Vain.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Maskaure Långmyran, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>617720</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7316234</v>
-      </c>
-      <c r="S57" t="n">
-        <v>6</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>135322939</v>
-      </c>
-      <c r="B58" t="n">
-        <v>80267</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>266179</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Lecidea subhumida</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Vain.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Maskaure Långmyran, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>617550</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7316331</v>
-      </c>
-      <c r="S58" t="n">
-        <v>9</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5355,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>96019502</v>
+        <v>135326163</v>
       </c>
       <c r="B45" t="n">
-        <v>78334</v>
+        <v>79992</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,37 +5366,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>617477</v>
+        <v>617613</v>
       </c>
       <c r="R45" t="n">
-        <v>7316220</v>
+        <v>7316170</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5420,42 +5420,57 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135322941</v>
+        <v>96019502</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>78334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5463,42 +5478,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>617391</v>
+        <v>617477</v>
       </c>
       <c r="R46" t="n">
-        <v>7316296</v>
+        <v>7316220</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5522,22 +5532,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:13</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:13</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5552,26 +5552,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135322928</v>
+        <v>135326174</v>
       </c>
       <c r="B47" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5579,46 +5575,45 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>617773</v>
+        <v>617512</v>
       </c>
       <c r="R47" t="n">
-        <v>7316117</v>
+        <v>7316190</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5647,7 +5642,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5657,14 +5652,19 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG47" t="b">
         <v>0</v>
@@ -5672,12 +5672,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5688,48 +5688,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135326169</v>
+        <v>135322941</v>
       </c>
       <c r="B48" t="n">
-        <v>98219</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219815</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>617380</v>
+        <v>617391</v>
       </c>
       <c r="R48" t="n">
-        <v>7316322</v>
+        <v>7316296</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5758,7 +5763,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5768,7 +5773,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5783,12 +5788,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5799,10 +5804,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135322932</v>
+        <v>135326171</v>
       </c>
       <c r="B49" t="n">
-        <v>78382</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5810,37 +5815,45 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>617752</v>
+        <v>617392</v>
       </c>
       <c r="R49" t="n">
-        <v>7316138</v>
+        <v>7316308</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5869,7 +5882,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5879,7 +5892,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5894,12 +5912,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5910,45 +5928,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135326166</v>
+        <v>135322928</v>
       </c>
       <c r="B50" t="n">
-        <v>78382</v>
+        <v>57162</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228579</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>617505</v>
+        <v>617773</v>
       </c>
       <c r="R50" t="n">
-        <v>7316325</v>
+        <v>7316117</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5980,7 +6007,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5990,7 +6017,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6005,12 +6032,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6021,32 +6048,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135326173</v>
+        <v>135326169</v>
       </c>
       <c r="B51" t="n">
-        <v>78382</v>
+        <v>98219</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>219815</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6056,13 +6083,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>617462</v>
+        <v>617380</v>
       </c>
       <c r="R51" t="n">
-        <v>7316207</v>
+        <v>7316322</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6091,7 +6118,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6101,7 +6128,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6132,10 +6159,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135322946</v>
+        <v>135322932</v>
       </c>
       <c r="B52" t="n">
-        <v>79963</v>
+        <v>78382</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6143,21 +6170,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>228579</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6167,13 +6194,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>617647</v>
+        <v>617752</v>
       </c>
       <c r="R52" t="n">
-        <v>7316156</v>
+        <v>7316138</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6202,7 +6229,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6212,7 +6239,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6243,10 +6270,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135322948</v>
+        <v>135326166</v>
       </c>
       <c r="B53" t="n">
-        <v>79396</v>
+        <v>78382</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6254,37 +6281,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>260591</v>
+        <v>228579</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>617649</v>
+        <v>617505</v>
       </c>
       <c r="R53" t="n">
-        <v>7316156</v>
+        <v>7316325</v>
       </c>
       <c r="S53" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6313,7 +6340,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6323,12 +6350,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Med gula soral</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6343,12 +6365,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6359,10 +6381,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135326162</v>
+        <v>135326173</v>
       </c>
       <c r="B54" t="n">
-        <v>79396</v>
+        <v>78382</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6370,21 +6392,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>260591</v>
+        <v>228579</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6394,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>617639</v>
+        <v>617462</v>
       </c>
       <c r="R54" t="n">
-        <v>7316143</v>
+        <v>7316207</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6429,7 +6451,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6439,7 +6461,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6470,27 +6492,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135322935</v>
+        <v>135322946</v>
       </c>
       <c r="B55" t="n">
-        <v>80267</v>
+        <v>79963</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>266179</v>
+        <v>229821</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6500,13 +6527,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>617720</v>
+        <v>617647</v>
       </c>
       <c r="R55" t="n">
-        <v>7316234</v>
+        <v>7316156</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6535,7 +6562,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6545,7 +6572,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6576,27 +6603,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135322939</v>
+        <v>135322948</v>
       </c>
       <c r="B56" t="n">
-        <v>80267</v>
+        <v>79396</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>266179</v>
+        <v>260591</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6606,13 +6638,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>617550</v>
+        <v>617649</v>
       </c>
       <c r="R56" t="n">
-        <v>7316331</v>
+        <v>7316156</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6641,7 +6673,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6651,7 +6683,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Med gula soral</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6675,6 +6712,329 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135326162</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>617639</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7316143</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135322935</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80267</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>617720</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7316234</v>
+      </c>
+      <c r="S58" t="n">
+        <v>6</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135322939</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80267</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>617550</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7316331</v>
+      </c>
+      <c r="S59" t="n">
+        <v>9</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2284,48 +2284,51 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96019471</v>
+        <v>135336170</v>
       </c>
       <c r="B17" t="n">
-        <v>92283</v>
+        <v>83363</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2063</v>
+        <v>1467</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>617488</v>
+        <v>617752</v>
       </c>
       <c r="R17" t="n">
-        <v>7316243</v>
+        <v>7316113</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2349,12 +2352,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,28 +2376,48 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>På barken av en björkstubbe # Betula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135325814</v>
+        <v>96019471</v>
       </c>
       <c r="B18" t="n">
-        <v>92320</v>
+        <v>92283</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,17 +2445,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>617583</v>
+        <v>617488</v>
       </c>
       <c r="R18" t="n">
-        <v>7316339</v>
+        <v>7316243</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,22 +2479,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2476,48 +2499,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135325815</v>
+        <v>135325814</v>
       </c>
       <c r="B19" t="n">
-        <v>92027</v>
+        <v>92320</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>2063</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2546,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>617465</v>
+        <v>617583</v>
       </c>
       <c r="R19" t="n">
-        <v>7316316</v>
+        <v>7316339</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2562,7 +2581,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2572,7 +2591,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,48 +2622,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96019501</v>
+        <v>135325815</v>
       </c>
       <c r="B20" t="n">
-        <v>92333</v>
+        <v>92027</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4217</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>617402</v>
+        <v>617465</v>
       </c>
       <c r="R20" t="n">
-        <v>7316257</v>
+        <v>7316316</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2668,17 +2687,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,44 +2717,48 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96019503</v>
+        <v>96019501</v>
       </c>
       <c r="B21" t="n">
-        <v>89156</v>
+        <v>92333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4412</v>
+        <v>4217</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2740,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617439</v>
+        <v>617402</v>
       </c>
       <c r="R21" t="n">
-        <v>7316241</v>
+        <v>7316257</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,6 +2804,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2802,48 +2835,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135322930</v>
+        <v>96019503</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>89156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617763</v>
+        <v>617439</v>
       </c>
       <c r="R22" t="n">
-        <v>7316118</v>
+        <v>7316241</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2867,22 +2900,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,23 +2920,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135322933</v>
+        <v>135322930</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2948,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617745</v>
+        <v>617763</v>
       </c>
       <c r="R23" t="n">
-        <v>7316136</v>
+        <v>7316118</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2983,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2993,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,7 +3043,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135325800</v>
+        <v>135322933</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3055,17 +3074,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617692</v>
+        <v>617745</v>
       </c>
       <c r="R24" t="n">
-        <v>7316206</v>
+        <v>7316136</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3094,7 +3113,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3104,7 +3123,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,12 +3138,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3135,7 +3154,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135325808</v>
+        <v>135325800</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3170,13 +3189,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>617658</v>
+        <v>617692</v>
       </c>
       <c r="R25" t="n">
-        <v>7316334</v>
+        <v>7316206</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3205,7 +3224,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3215,7 +3234,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,7 +3265,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135325820</v>
+        <v>135325808</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3281,13 +3300,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>617505</v>
+        <v>617658</v>
       </c>
       <c r="R26" t="n">
-        <v>7316297</v>
+        <v>7316334</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3316,7 +3335,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3326,7 +3345,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3357,32 +3376,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135325824</v>
+        <v>135325820</v>
       </c>
       <c r="B27" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3392,13 +3411,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>617617</v>
+        <v>617505</v>
       </c>
       <c r="R27" t="n">
-        <v>7316184</v>
+        <v>7316297</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3427,7 +3446,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3437,7 +3456,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,7 +3487,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135326164</v>
+        <v>135325824</v>
       </c>
       <c r="B28" t="n">
         <v>78776</v>
@@ -3499,14 +3518,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>617552</v>
+        <v>617617</v>
       </c>
       <c r="R28" t="n">
-        <v>7316225</v>
+        <v>7316184</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3538,7 +3557,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3548,7 +3567,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,12 +3582,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3579,10 +3598,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135322133</v>
+        <v>135326164</v>
       </c>
       <c r="B29" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3590,34 +3609,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>617704</v>
+        <v>617552</v>
       </c>
       <c r="R29" t="n">
-        <v>7316223</v>
+        <v>7316225</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3649,7 +3668,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3678,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,12 +3693,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3690,7 +3709,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135322927</v>
+        <v>135322133</v>
       </c>
       <c r="B30" t="n">
         <v>83358</v>
@@ -3721,14 +3740,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617778</v>
+        <v>617704</v>
       </c>
       <c r="R30" t="n">
-        <v>7316112</v>
+        <v>7316223</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3760,7 +3779,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3770,7 +3789,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3785,12 +3804,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3801,7 +3820,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135322940</v>
+        <v>135322927</v>
       </c>
       <c r="B31" t="n">
         <v>83358</v>
@@ -3836,13 +3855,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617520</v>
+        <v>617778</v>
       </c>
       <c r="R31" t="n">
-        <v>7316320</v>
+        <v>7316112</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3871,7 +3890,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3881,7 +3900,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3912,7 +3931,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135325798</v>
+        <v>135322940</v>
       </c>
       <c r="B32" t="n">
         <v>83358</v>
@@ -3943,17 +3962,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>617722</v>
+        <v>617520</v>
       </c>
       <c r="R32" t="n">
-        <v>7316104</v>
+        <v>7316320</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3982,7 +4001,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3992,7 +4011,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4007,12 +4026,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4023,7 +4042,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135325799</v>
+        <v>135325798</v>
       </c>
       <c r="B33" t="n">
         <v>83358</v>
@@ -4058,13 +4077,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>617701</v>
+        <v>617722</v>
       </c>
       <c r="R33" t="n">
-        <v>7316164</v>
+        <v>7316104</v>
       </c>
       <c r="S33" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4093,7 +4112,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4103,7 +4122,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4134,7 +4153,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135325801</v>
+        <v>135325799</v>
       </c>
       <c r="B34" t="n">
         <v>83358</v>
@@ -4169,13 +4188,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>617709</v>
+        <v>617701</v>
       </c>
       <c r="R34" t="n">
-        <v>7316204</v>
+        <v>7316164</v>
       </c>
       <c r="S34" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4204,7 +4223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4214,7 +4233,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4245,7 +4264,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135325805</v>
+        <v>135325801</v>
       </c>
       <c r="B35" t="n">
         <v>83358</v>
@@ -4280,13 +4299,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617678</v>
+        <v>617709</v>
       </c>
       <c r="R35" t="n">
-        <v>7316280</v>
+        <v>7316204</v>
       </c>
       <c r="S35" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4315,7 +4334,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4325,7 +4344,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4356,7 +4375,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135325813</v>
+        <v>135325805</v>
       </c>
       <c r="B36" t="n">
         <v>83358</v>
@@ -4391,13 +4410,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617583</v>
+        <v>617678</v>
       </c>
       <c r="R36" t="n">
-        <v>7316339</v>
+        <v>7316280</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4426,7 +4445,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4436,7 +4455,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4467,10 +4486,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135322137</v>
+        <v>135325813</v>
       </c>
       <c r="B37" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4478,37 +4497,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>617622</v>
+        <v>617583</v>
       </c>
       <c r="R37" t="n">
-        <v>7316280</v>
+        <v>7316339</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4537,7 +4556,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4547,7 +4566,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4562,12 +4581,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4578,7 +4597,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135322138</v>
+        <v>135322137</v>
       </c>
       <c r="B38" t="n">
         <v>79992</v>
@@ -4613,10 +4632,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>617729</v>
+        <v>617622</v>
       </c>
       <c r="R38" t="n">
-        <v>7316047</v>
+        <v>7316280</v>
       </c>
       <c r="S38" t="n">
         <v>6</v>
@@ -4648,7 +4667,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4658,7 +4677,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4689,7 +4708,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135322139</v>
+        <v>135322138</v>
       </c>
       <c r="B39" t="n">
         <v>79992</v>
@@ -4724,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617634</v>
+        <v>617729</v>
       </c>
       <c r="R39" t="n">
-        <v>7316176</v>
+        <v>7316047</v>
       </c>
       <c r="S39" t="n">
         <v>6</v>
@@ -4800,7 +4819,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135322945</v>
+        <v>135322139</v>
       </c>
       <c r="B40" t="n">
         <v>79992</v>
@@ -4831,17 +4850,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617566</v>
+        <v>617634</v>
       </c>
       <c r="R40" t="n">
-        <v>7316256</v>
+        <v>7316176</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4889,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4899,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4895,12 +4914,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4911,7 +4930,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135325797</v>
+        <v>135322945</v>
       </c>
       <c r="B41" t="n">
         <v>79992</v>
@@ -4942,17 +4961,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>617722</v>
+        <v>617566</v>
       </c>
       <c r="R41" t="n">
-        <v>7316104</v>
+        <v>7316256</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4981,7 +5000,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4991,7 +5010,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5006,12 +5025,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5022,7 +5041,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135325811</v>
+        <v>135325797</v>
       </c>
       <c r="B42" t="n">
         <v>79992</v>
@@ -5057,13 +5076,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>617596</v>
+        <v>617722</v>
       </c>
       <c r="R42" t="n">
-        <v>7316363</v>
+        <v>7316104</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5092,7 +5111,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5102,7 +5121,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5133,7 +5152,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135325821</v>
+        <v>135325811</v>
       </c>
       <c r="B43" t="n">
         <v>79992</v>
@@ -5168,13 +5187,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>617586</v>
+        <v>617596</v>
       </c>
       <c r="R43" t="n">
-        <v>7316239</v>
+        <v>7316363</v>
       </c>
       <c r="S43" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5203,7 +5222,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5213,7 +5232,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5244,7 +5263,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135325825</v>
+        <v>135325821</v>
       </c>
       <c r="B44" t="n">
         <v>79992</v>
@@ -5279,13 +5298,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>617617</v>
+        <v>617586</v>
       </c>
       <c r="R44" t="n">
-        <v>7316184</v>
+        <v>7316239</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5314,7 +5333,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5324,7 +5343,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5355,7 +5374,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135326163</v>
+        <v>135325825</v>
       </c>
       <c r="B45" t="n">
         <v>79992</v>
@@ -5386,17 +5405,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>617613</v>
+        <v>617617</v>
       </c>
       <c r="R45" t="n">
-        <v>7316170</v>
+        <v>7316184</v>
       </c>
       <c r="S45" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5425,7 +5444,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5435,28 +5454,27 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5467,10 +5485,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>96019502</v>
+        <v>135326163</v>
       </c>
       <c r="B46" t="n">
-        <v>78334</v>
+        <v>79992</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5478,37 +5496,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>617477</v>
+        <v>617613</v>
       </c>
       <c r="R46" t="n">
-        <v>7316220</v>
+        <v>7316170</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5532,88 +5550,95 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135326174</v>
+        <v>135336181</v>
       </c>
       <c r="B47" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>617512</v>
+        <v>617647</v>
       </c>
       <c r="R47" t="n">
-        <v>7316190</v>
+        <v>7316156</v>
       </c>
       <c r="S47" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5642,7 +5667,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5652,32 +5677,42 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Födosök.</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Gammal tallrotvälta # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5688,10 +5723,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135322941</v>
+        <v>96019502</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>78334</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5699,42 +5734,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>617391</v>
+        <v>617477</v>
       </c>
       <c r="R48" t="n">
-        <v>7316296</v>
+        <v>7316220</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5758,22 +5788,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:13</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:13</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5788,43 +5808,39 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135326171</v>
+        <v>135326174</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5847,13 +5863,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>617392</v>
+        <v>617512</v>
       </c>
       <c r="R49" t="n">
-        <v>7316308</v>
+        <v>7316190</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5882,7 +5898,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5892,19 +5908,19 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG49" t="b">
         <v>0</v>
@@ -5928,42 +5944,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135322928</v>
+        <v>135322941</v>
       </c>
       <c r="B50" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5972,10 +5984,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>617773</v>
+        <v>617391</v>
       </c>
       <c r="R50" t="n">
-        <v>7316117</v>
+        <v>7316296</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6007,7 +6019,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6017,7 +6029,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6048,48 +6060,56 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135326169</v>
+        <v>135326171</v>
       </c>
       <c r="B51" t="n">
-        <v>98219</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219815</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>617380</v>
+        <v>617392</v>
       </c>
       <c r="R51" t="n">
-        <v>7316322</v>
+        <v>7316308</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6118,7 +6138,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6128,7 +6148,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6159,45 +6184,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135322932</v>
+        <v>135322928</v>
       </c>
       <c r="B52" t="n">
-        <v>78382</v>
+        <v>57162</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228579</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>617752</v>
+        <v>617773</v>
       </c>
       <c r="R52" t="n">
-        <v>7316138</v>
+        <v>7316117</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6229,7 +6263,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6239,7 +6273,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6270,45 +6304,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135326166</v>
+        <v>135336171</v>
       </c>
       <c r="B53" t="n">
-        <v>78382</v>
+        <v>5201</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>617505</v>
+        <v>617710</v>
       </c>
       <c r="R53" t="n">
-        <v>7316325</v>
+        <v>7316168</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6340,7 +6374,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6350,7 +6384,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6361,16 +6395,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6381,45 +6430,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135326173</v>
+        <v>135336178</v>
       </c>
       <c r="B54" t="n">
-        <v>78382</v>
+        <v>5201</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228579</v>
+        <v>105930</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>617462</v>
+        <v>617577</v>
       </c>
       <c r="R54" t="n">
-        <v>7316207</v>
+        <v>7316342</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6451,7 +6500,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6461,7 +6510,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6472,16 +6521,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Klen granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6492,10 +6556,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135322946</v>
+        <v>135336168</v>
       </c>
       <c r="B55" t="n">
-        <v>79963</v>
+        <v>41606</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6503,34 +6567,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>215713</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>617647</v>
+        <v>617763</v>
       </c>
       <c r="R55" t="n">
-        <v>7316156</v>
+        <v>7316087</v>
       </c>
       <c r="S55" t="n">
         <v>7</v>
@@ -6562,7 +6631,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6572,7 +6641,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6587,12 +6656,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6603,48 +6672,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135322948</v>
+        <v>135326169</v>
       </c>
       <c r="B56" t="n">
-        <v>79396</v>
+        <v>98219</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>260591</v>
+        <v>219815</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>617649</v>
+        <v>617380</v>
       </c>
       <c r="R56" t="n">
-        <v>7316156</v>
+        <v>7316322</v>
       </c>
       <c r="S56" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6673,7 +6742,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6683,12 +6752,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Med gula soral</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6703,12 +6767,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6719,45 +6783,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135326162</v>
+        <v>135336172</v>
       </c>
       <c r="B57" t="n">
-        <v>79396</v>
+        <v>110023</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>260591</v>
+        <v>220263</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Fjällskråp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Petasites frigidus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>617639</v>
+        <v>617694</v>
       </c>
       <c r="R57" t="n">
-        <v>7316143</v>
+        <v>7316205</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6789,7 +6853,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6799,7 +6863,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6814,12 +6878,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6830,43 +6894,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135322935</v>
+        <v>135336176</v>
       </c>
       <c r="B58" t="n">
-        <v>80267</v>
+        <v>99217</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>266179</v>
+        <v>221952</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>617720</v>
+        <v>617684</v>
       </c>
       <c r="R58" t="n">
-        <v>7316234</v>
+        <v>7316239</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6895,7 +6964,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6905,7 +6974,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6920,12 +6989,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6936,27 +7005,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135322939</v>
+        <v>135322932</v>
       </c>
       <c r="B59" t="n">
-        <v>80267</v>
+        <v>78382</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>266179</v>
+        <v>228579</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6966,13 +7040,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>617550</v>
+        <v>617752</v>
       </c>
       <c r="R59" t="n">
-        <v>7316331</v>
+        <v>7316138</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7001,7 +7075,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7011,7 +7085,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7035,6 +7109,778 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135326166</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>617505</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7316325</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135326173</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>617462</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7316207</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135322946</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>617647</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7316156</v>
+      </c>
+      <c r="S62" t="n">
+        <v>7</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135322948</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>617649</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7316156</v>
+      </c>
+      <c r="S63" t="n">
+        <v>14</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Med gula soral</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135326162</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>617639</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7316143</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135322935</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80267</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>617720</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7316234</v>
+      </c>
+      <c r="S65" t="n">
+        <v>6</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135322939</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80267</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>617550</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7316331</v>
+      </c>
+      <c r="S66" t="n">
+        <v>9</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2733,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96019501</v>
+        <v>135336173</v>
       </c>
       <c r="B21" t="n">
-        <v>92333</v>
+        <v>96389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2744,37 +2744,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4217</v>
+        <v>2664</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Klomossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dichelyma falcatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Myrin</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617402</v>
+        <v>617689</v>
       </c>
       <c r="R21" t="n">
-        <v>7316257</v>
+        <v>7316215</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2798,17 +2802,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2817,50 +2826,55 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96019503</v>
+        <v>96019501</v>
       </c>
       <c r="B22" t="n">
-        <v>89156</v>
+        <v>92333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>4217</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2884,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617439</v>
+        <v>617402</v>
       </c>
       <c r="R22" t="n">
-        <v>7316241</v>
+        <v>7316257</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,6 +2920,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2932,48 +2951,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135322930</v>
+        <v>96019503</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>89156</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617763</v>
+        <v>617439</v>
       </c>
       <c r="R23" t="n">
-        <v>7316118</v>
+        <v>7316241</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2997,22 +3016,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,23 +3036,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135322933</v>
+        <v>135322930</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3078,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617745</v>
+        <v>617763</v>
       </c>
       <c r="R24" t="n">
-        <v>7316136</v>
+        <v>7316118</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,7 +3118,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3123,7 +3128,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,7 +3159,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135325800</v>
+        <v>135322933</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3185,17 +3190,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>617692</v>
+        <v>617745</v>
       </c>
       <c r="R25" t="n">
-        <v>7316206</v>
+        <v>7316136</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3224,7 +3229,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3234,7 +3239,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3249,12 +3254,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3265,7 +3270,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135325808</v>
+        <v>135325800</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3300,13 +3305,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>617658</v>
+        <v>617692</v>
       </c>
       <c r="R26" t="n">
-        <v>7316334</v>
+        <v>7316206</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3335,7 +3340,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3345,7 +3350,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3376,7 +3381,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135325820</v>
+        <v>135325808</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3411,13 +3416,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>617505</v>
+        <v>617658</v>
       </c>
       <c r="R27" t="n">
-        <v>7316297</v>
+        <v>7316334</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3446,7 +3451,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3456,7 +3461,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3487,32 +3492,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135325824</v>
+        <v>135325820</v>
       </c>
       <c r="B28" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3522,13 +3527,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>617617</v>
+        <v>617505</v>
       </c>
       <c r="R28" t="n">
-        <v>7316184</v>
+        <v>7316297</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3557,7 +3562,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3567,7 +3572,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3598,7 +3603,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135326164</v>
+        <v>135325824</v>
       </c>
       <c r="B29" t="n">
         <v>78776</v>
@@ -3629,14 +3634,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>617552</v>
+        <v>617617</v>
       </c>
       <c r="R29" t="n">
-        <v>7316225</v>
+        <v>7316184</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3668,7 +3673,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3678,7 +3683,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3693,12 +3698,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3709,10 +3714,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135322133</v>
+        <v>135326164</v>
       </c>
       <c r="B30" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,34 +3725,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617704</v>
+        <v>617552</v>
       </c>
       <c r="R30" t="n">
-        <v>7316223</v>
+        <v>7316225</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3779,7 +3784,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3789,7 +3794,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3804,12 +3809,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3820,7 +3825,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135322927</v>
+        <v>135322133</v>
       </c>
       <c r="B31" t="n">
         <v>83358</v>
@@ -3851,14 +3856,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617778</v>
+        <v>617704</v>
       </c>
       <c r="R31" t="n">
-        <v>7316112</v>
+        <v>7316223</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3890,7 +3895,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3900,7 +3905,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,12 +3920,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3931,7 +3936,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135322940</v>
+        <v>135322927</v>
       </c>
       <c r="B32" t="n">
         <v>83358</v>
@@ -3966,13 +3971,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>617520</v>
+        <v>617778</v>
       </c>
       <c r="R32" t="n">
-        <v>7316320</v>
+        <v>7316112</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4001,7 +4006,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4011,7 +4016,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,7 +4047,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135325798</v>
+        <v>135322940</v>
       </c>
       <c r="B33" t="n">
         <v>83358</v>
@@ -4073,17 +4078,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>617722</v>
+        <v>617520</v>
       </c>
       <c r="R33" t="n">
-        <v>7316104</v>
+        <v>7316320</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4112,7 +4117,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4122,7 +4127,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,12 +4142,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4153,7 +4158,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135325799</v>
+        <v>135325798</v>
       </c>
       <c r="B34" t="n">
         <v>83358</v>
@@ -4188,13 +4193,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>617701</v>
+        <v>617722</v>
       </c>
       <c r="R34" t="n">
-        <v>7316164</v>
+        <v>7316104</v>
       </c>
       <c r="S34" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4223,7 +4228,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4233,7 +4238,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4264,7 +4269,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135325801</v>
+        <v>135325799</v>
       </c>
       <c r="B35" t="n">
         <v>83358</v>
@@ -4299,13 +4304,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617709</v>
+        <v>617701</v>
       </c>
       <c r="R35" t="n">
-        <v>7316204</v>
+        <v>7316164</v>
       </c>
       <c r="S35" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4334,7 +4339,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4344,7 +4349,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4375,7 +4380,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135325805</v>
+        <v>135325801</v>
       </c>
       <c r="B36" t="n">
         <v>83358</v>
@@ -4410,13 +4415,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617678</v>
+        <v>617709</v>
       </c>
       <c r="R36" t="n">
-        <v>7316280</v>
+        <v>7316204</v>
       </c>
       <c r="S36" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4445,7 +4450,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4455,7 +4460,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4486,7 +4491,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135325813</v>
+        <v>135325805</v>
       </c>
       <c r="B37" t="n">
         <v>83358</v>
@@ -4521,13 +4526,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>617583</v>
+        <v>617678</v>
       </c>
       <c r="R37" t="n">
-        <v>7316339</v>
+        <v>7316280</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4556,7 +4561,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4566,7 +4571,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4597,10 +4602,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135322137</v>
+        <v>135325813</v>
       </c>
       <c r="B38" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4608,37 +4613,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>617622</v>
+        <v>617583</v>
       </c>
       <c r="R38" t="n">
-        <v>7316280</v>
+        <v>7316339</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4667,7 +4672,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4677,7 +4682,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4692,12 +4697,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4708,7 +4713,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135322138</v>
+        <v>135322137</v>
       </c>
       <c r="B39" t="n">
         <v>79992</v>
@@ -4743,10 +4748,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617729</v>
+        <v>617622</v>
       </c>
       <c r="R39" t="n">
-        <v>7316047</v>
+        <v>7316280</v>
       </c>
       <c r="S39" t="n">
         <v>6</v>
@@ -4778,7 +4783,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4788,7 +4793,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4819,7 +4824,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135322139</v>
+        <v>135322138</v>
       </c>
       <c r="B40" t="n">
         <v>79992</v>
@@ -4854,10 +4859,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617634</v>
+        <v>617729</v>
       </c>
       <c r="R40" t="n">
-        <v>7316176</v>
+        <v>7316047</v>
       </c>
       <c r="S40" t="n">
         <v>6</v>
@@ -4930,7 +4935,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135322945</v>
+        <v>135322139</v>
       </c>
       <c r="B41" t="n">
         <v>79992</v>
@@ -4961,17 +4966,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>617566</v>
+        <v>617634</v>
       </c>
       <c r="R41" t="n">
-        <v>7316256</v>
+        <v>7316176</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5000,7 +5005,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5010,7 +5015,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5025,12 +5030,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5041,7 +5046,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135325797</v>
+        <v>135322945</v>
       </c>
       <c r="B42" t="n">
         <v>79992</v>
@@ -5072,17 +5077,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>617722</v>
+        <v>617566</v>
       </c>
       <c r="R42" t="n">
-        <v>7316104</v>
+        <v>7316256</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5111,7 +5116,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5121,7 +5126,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5136,12 +5141,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5152,7 +5157,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135325811</v>
+        <v>135325797</v>
       </c>
       <c r="B43" t="n">
         <v>79992</v>
@@ -5187,13 +5192,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>617596</v>
+        <v>617722</v>
       </c>
       <c r="R43" t="n">
-        <v>7316363</v>
+        <v>7316104</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5222,7 +5227,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5232,7 +5237,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5263,7 +5268,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135325821</v>
+        <v>135325811</v>
       </c>
       <c r="B44" t="n">
         <v>79992</v>
@@ -5298,13 +5303,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>617586</v>
+        <v>617596</v>
       </c>
       <c r="R44" t="n">
-        <v>7316239</v>
+        <v>7316363</v>
       </c>
       <c r="S44" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5333,7 +5338,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5343,7 +5348,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5374,7 +5379,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135325825</v>
+        <v>135325821</v>
       </c>
       <c r="B45" t="n">
         <v>79992</v>
@@ -5409,13 +5414,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>617617</v>
+        <v>617586</v>
       </c>
       <c r="R45" t="n">
-        <v>7316184</v>
+        <v>7316239</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5444,7 +5449,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5454,7 +5459,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5485,7 +5490,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135326163</v>
+        <v>135325825</v>
       </c>
       <c r="B46" t="n">
         <v>79992</v>
@@ -5516,17 +5521,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>617613</v>
+        <v>617617</v>
       </c>
       <c r="R46" t="n">
-        <v>7316170</v>
+        <v>7316184</v>
       </c>
       <c r="S46" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5555,7 +5560,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5565,28 +5570,27 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5597,7 +5601,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135336181</v>
+        <v>135326163</v>
       </c>
       <c r="B47" t="n">
         <v>79992</v>
@@ -5628,17 +5632,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Maskaure, Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>617647</v>
+        <v>617613</v>
       </c>
       <c r="R47" t="n">
-        <v>7316156</v>
+        <v>7316170</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5667,7 +5671,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5677,42 +5681,28 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Gammal tallrotvälta # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5723,10 +5713,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>96019502</v>
+        <v>135336181</v>
       </c>
       <c r="B48" t="n">
-        <v>78334</v>
+        <v>79992</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5734,37 +5724,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>617477</v>
+        <v>617647</v>
       </c>
       <c r="R48" t="n">
-        <v>7316220</v>
+        <v>7316156</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5788,12 +5778,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5804,72 +5804,83 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Gammal tallrotvälta # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135326174</v>
+        <v>96019502</v>
       </c>
       <c r="B49" t="n">
-        <v>57972</v>
+        <v>78334</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>617512</v>
+        <v>617477</v>
       </c>
       <c r="R49" t="n">
-        <v>7316190</v>
+        <v>7316220</v>
       </c>
       <c r="S49" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5893,34 +5904,19 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Födosök.</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="b">
         <v>0</v>
@@ -5928,43 +5924,39 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135322941</v>
+        <v>135326174</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5973,24 +5965,27 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>617391</v>
+        <v>617512</v>
       </c>
       <c r="R50" t="n">
-        <v>7316296</v>
+        <v>7316190</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6019,7 +6014,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6029,14 +6024,19 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG50" t="b">
         <v>0</v>
@@ -6044,12 +6044,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6060,7 +6060,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135326171</v>
+        <v>135322941</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -6089,27 +6089,24 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>617392</v>
+        <v>617391</v>
       </c>
       <c r="R51" t="n">
-        <v>7316308</v>
+        <v>7316296</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6138,7 +6135,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6148,12 +6145,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6168,12 +6160,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6184,57 +6176,56 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135322928</v>
+        <v>135326171</v>
       </c>
       <c r="B52" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>617773</v>
+        <v>617392</v>
       </c>
       <c r="R52" t="n">
-        <v>7316117</v>
+        <v>7316308</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6263,7 +6254,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6273,7 +6264,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6288,12 +6284,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6304,10 +6300,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135336171</v>
+        <v>135322928</v>
       </c>
       <c r="B53" t="n">
-        <v>5201</v>
+        <v>57162</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6315,34 +6311,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Maskaure, Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>617710</v>
+        <v>617773</v>
       </c>
       <c r="R53" t="n">
-        <v>7316168</v>
+        <v>7316117</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6374,7 +6379,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6384,7 +6389,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6395,31 +6400,16 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6430,7 +6420,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135336178</v>
+        <v>135336171</v>
       </c>
       <c r="B54" t="n">
         <v>5201</v>
@@ -6465,10 +6455,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>617577</v>
+        <v>617710</v>
       </c>
       <c r="R54" t="n">
-        <v>7316342</v>
+        <v>7316168</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6500,7 +6490,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6510,7 +6500,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6534,7 +6524,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Klen granlåga # Picea abies</t>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6556,53 +6546,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135336168</v>
+        <v>135336178</v>
       </c>
       <c r="B55" t="n">
-        <v>41606</v>
+        <v>5201</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>215713</v>
+        <v>105930</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>617763</v>
+        <v>617577</v>
       </c>
       <c r="R55" t="n">
-        <v>7316087</v>
+        <v>7316342</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6631,7 +6616,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6641,7 +6626,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6652,6 +6637,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Klen granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6672,48 +6672,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135326169</v>
+        <v>135336168</v>
       </c>
       <c r="B56" t="n">
-        <v>98219</v>
+        <v>41606</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219815</v>
+        <v>215713</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>617380</v>
+        <v>617763</v>
       </c>
       <c r="R56" t="n">
-        <v>7316322</v>
+        <v>7316087</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6742,7 +6747,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6752,7 +6757,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6767,12 +6772,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6783,10 +6788,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135336172</v>
+        <v>135326169</v>
       </c>
       <c r="B57" t="n">
-        <v>110023</v>
+        <v>98219</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6794,37 +6799,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220263</v>
+        <v>219815</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällskråp</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Petasites frigidus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Maskaure, Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>617694</v>
+        <v>617380</v>
       </c>
       <c r="R57" t="n">
-        <v>7316205</v>
+        <v>7316322</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6853,7 +6858,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6863,7 +6868,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6878,12 +6883,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6894,10 +6899,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135336176</v>
+        <v>135336172</v>
       </c>
       <c r="B58" t="n">
-        <v>99217</v>
+        <v>110023</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6905,21 +6910,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>220263</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fjällskråp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Petasites frigidus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6929,10 +6934,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>617684</v>
+        <v>617694</v>
       </c>
       <c r="R58" t="n">
-        <v>7316239</v>
+        <v>7316205</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6964,7 +6969,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6974,7 +6979,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7005,45 +7010,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135322932</v>
+        <v>135336176</v>
       </c>
       <c r="B59" t="n">
-        <v>78382</v>
+        <v>99217</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>617752</v>
+        <v>617684</v>
       </c>
       <c r="R59" t="n">
-        <v>7316138</v>
+        <v>7316239</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7075,7 +7080,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7085,7 +7090,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7100,12 +7105,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7116,7 +7121,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135326166</v>
+        <v>135322932</v>
       </c>
       <c r="B60" t="n">
         <v>78382</v>
@@ -7147,14 +7152,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>617505</v>
+        <v>617752</v>
       </c>
       <c r="R60" t="n">
-        <v>7316325</v>
+        <v>7316138</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7186,7 +7191,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7196,7 +7201,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7211,12 +7216,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7227,7 +7232,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135326173</v>
+        <v>135326166</v>
       </c>
       <c r="B61" t="n">
         <v>78382</v>
@@ -7262,10 +7267,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>617462</v>
+        <v>617505</v>
       </c>
       <c r="R61" t="n">
-        <v>7316207</v>
+        <v>7316325</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7297,7 +7302,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7307,7 +7312,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7338,10 +7343,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135322946</v>
+        <v>135326173</v>
       </c>
       <c r="B62" t="n">
-        <v>79963</v>
+        <v>78382</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7349,37 +7354,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>617647</v>
+        <v>617462</v>
       </c>
       <c r="R62" t="n">
-        <v>7316156</v>
+        <v>7316207</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7408,7 +7413,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7418,7 +7423,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7433,12 +7438,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7449,10 +7454,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135322948</v>
+        <v>135322946</v>
       </c>
       <c r="B63" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7460,21 +7465,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7484,13 +7489,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>617649</v>
+        <v>617647</v>
       </c>
       <c r="R63" t="n">
         <v>7316156</v>
       </c>
       <c r="S63" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7519,7 +7524,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7529,12 +7534,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Med gula soral</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7565,7 +7565,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135326162</v>
+        <v>135322948</v>
       </c>
       <c r="B64" t="n">
         <v>79396</v>
@@ -7596,17 +7596,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>617639</v>
+        <v>617649</v>
       </c>
       <c r="R64" t="n">
-        <v>7316143</v>
+        <v>7316156</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7645,7 +7645,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Med gula soral</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7660,12 +7665,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7676,43 +7681,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135322935</v>
+        <v>135326162</v>
       </c>
       <c r="B65" t="n">
-        <v>80267</v>
+        <v>79396</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>266179</v>
+        <v>260591</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>617720</v>
+        <v>617639</v>
       </c>
       <c r="R65" t="n">
-        <v>7316234</v>
+        <v>7316143</v>
       </c>
       <c r="S65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7741,7 +7751,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7751,7 +7761,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7766,12 +7776,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7782,7 +7792,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135322939</v>
+        <v>135322935</v>
       </c>
       <c r="B66" t="n">
         <v>80267</v>
@@ -7812,13 +7822,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>617550</v>
+        <v>617720</v>
       </c>
       <c r="R66" t="n">
-        <v>7316331</v>
+        <v>7316234</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7847,7 +7857,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7857,7 +7867,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7881,6 +7891,112 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135322939</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80267</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>617550</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7316331</v>
+      </c>
+      <c r="S67" t="n">
+        <v>9</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2733,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135336173</v>
+        <v>96019501</v>
       </c>
       <c r="B21" t="n">
-        <v>96389</v>
+        <v>92333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2744,41 +2744,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2664</v>
+        <v>4217</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Klomossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dichelyma falcatum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Myrin</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Maskaure, Långmyran, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617689</v>
+        <v>617402</v>
       </c>
       <c r="R21" t="n">
-        <v>7316215</v>
+        <v>7316257</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2802,22 +2798,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2826,55 +2817,50 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96019501</v>
+        <v>96019503</v>
       </c>
       <c r="B22" t="n">
-        <v>92333</v>
+        <v>89156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4217</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2884,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617402</v>
+        <v>617439</v>
       </c>
       <c r="R22" t="n">
-        <v>7316257</v>
+        <v>7316241</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,11 +2906,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,48 +2932,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96019503</v>
+        <v>135322930</v>
       </c>
       <c r="B23" t="n">
-        <v>89156</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617439</v>
+        <v>617763</v>
       </c>
       <c r="R23" t="n">
-        <v>7316241</v>
+        <v>7316118</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3016,12 +2997,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,19 +3027,23 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135322930</v>
+        <v>135322933</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3083,10 +3078,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617763</v>
+        <v>617745</v>
       </c>
       <c r="R24" t="n">
-        <v>7316118</v>
+        <v>7316136</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3118,7 +3113,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3128,7 +3123,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,7 +3154,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135322933</v>
+        <v>135325800</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3190,17 +3185,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>617745</v>
+        <v>617692</v>
       </c>
       <c r="R25" t="n">
-        <v>7316136</v>
+        <v>7316206</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3229,7 +3224,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3239,7 +3234,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3254,12 +3249,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3270,7 +3265,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135325800</v>
+        <v>135325808</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3305,13 +3300,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>617692</v>
+        <v>617658</v>
       </c>
       <c r="R26" t="n">
-        <v>7316206</v>
+        <v>7316334</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3340,7 +3335,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3350,7 +3345,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3381,7 +3376,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135325808</v>
+        <v>135325820</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3416,13 +3411,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>617658</v>
+        <v>617505</v>
       </c>
       <c r="R27" t="n">
-        <v>7316334</v>
+        <v>7316297</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3451,7 +3446,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3461,7 +3456,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3492,32 +3487,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135325820</v>
+        <v>135325824</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>78776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3527,13 +3522,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>617505</v>
+        <v>617617</v>
       </c>
       <c r="R28" t="n">
-        <v>7316297</v>
+        <v>7316184</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3562,7 +3557,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3572,7 +3567,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,7 +3598,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135325824</v>
+        <v>135326164</v>
       </c>
       <c r="B29" t="n">
         <v>78776</v>
@@ -3634,14 +3629,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>617617</v>
+        <v>617552</v>
       </c>
       <c r="R29" t="n">
-        <v>7316184</v>
+        <v>7316225</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3673,7 +3668,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3683,7 +3678,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3698,12 +3693,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3714,10 +3709,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135326164</v>
+        <v>135322133</v>
       </c>
       <c r="B30" t="n">
-        <v>78776</v>
+        <v>83358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3725,34 +3720,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617552</v>
+        <v>617704</v>
       </c>
       <c r="R30" t="n">
-        <v>7316225</v>
+        <v>7316223</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3784,7 +3779,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3794,7 +3789,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3809,12 +3804,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3825,7 +3820,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135322133</v>
+        <v>135322927</v>
       </c>
       <c r="B31" t="n">
         <v>83358</v>
@@ -3856,14 +3851,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617704</v>
+        <v>617778</v>
       </c>
       <c r="R31" t="n">
-        <v>7316223</v>
+        <v>7316112</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3895,7 +3890,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3905,7 +3900,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3920,12 +3915,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3936,7 +3931,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135322927</v>
+        <v>135322940</v>
       </c>
       <c r="B32" t="n">
         <v>83358</v>
@@ -3971,13 +3966,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>617778</v>
+        <v>617520</v>
       </c>
       <c r="R32" t="n">
-        <v>7316112</v>
+        <v>7316320</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4006,7 +4001,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4016,7 +4011,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4047,7 +4042,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135322940</v>
+        <v>135325798</v>
       </c>
       <c r="B33" t="n">
         <v>83358</v>
@@ -4078,17 +4073,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>617520</v>
+        <v>617722</v>
       </c>
       <c r="R33" t="n">
-        <v>7316320</v>
+        <v>7316104</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4117,7 +4112,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4127,7 +4122,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4142,12 +4137,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4158,7 +4153,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135325798</v>
+        <v>135325799</v>
       </c>
       <c r="B34" t="n">
         <v>83358</v>
@@ -4193,13 +4188,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>617722</v>
+        <v>617701</v>
       </c>
       <c r="R34" t="n">
-        <v>7316104</v>
+        <v>7316164</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4228,7 +4223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4238,7 +4233,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4269,7 +4264,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135325799</v>
+        <v>135325801</v>
       </c>
       <c r="B35" t="n">
         <v>83358</v>
@@ -4304,13 +4299,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617701</v>
+        <v>617709</v>
       </c>
       <c r="R35" t="n">
-        <v>7316164</v>
+        <v>7316204</v>
       </c>
       <c r="S35" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4339,7 +4334,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4349,7 +4344,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4380,7 +4375,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135325801</v>
+        <v>135325805</v>
       </c>
       <c r="B36" t="n">
         <v>83358</v>
@@ -4415,13 +4410,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617709</v>
+        <v>617678</v>
       </c>
       <c r="R36" t="n">
-        <v>7316204</v>
+        <v>7316280</v>
       </c>
       <c r="S36" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4450,7 +4445,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4460,7 +4455,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4491,7 +4486,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135325805</v>
+        <v>135325813</v>
       </c>
       <c r="B37" t="n">
         <v>83358</v>
@@ -4526,13 +4521,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>617678</v>
+        <v>617583</v>
       </c>
       <c r="R37" t="n">
-        <v>7316280</v>
+        <v>7316339</v>
       </c>
       <c r="S37" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4561,7 +4556,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4571,7 +4566,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4602,10 +4597,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135325813</v>
+        <v>135322137</v>
       </c>
       <c r="B38" t="n">
-        <v>83358</v>
+        <v>79992</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4613,37 +4608,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>617583</v>
+        <v>617622</v>
       </c>
       <c r="R38" t="n">
-        <v>7316339</v>
+        <v>7316280</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4672,7 +4667,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4682,7 +4677,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4697,12 +4692,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4713,7 +4708,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135322137</v>
+        <v>135322138</v>
       </c>
       <c r="B39" t="n">
         <v>79992</v>
@@ -4748,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617622</v>
+        <v>617729</v>
       </c>
       <c r="R39" t="n">
-        <v>7316280</v>
+        <v>7316047</v>
       </c>
       <c r="S39" t="n">
         <v>6</v>
@@ -4783,7 +4778,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4793,7 +4788,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4824,7 +4819,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135322138</v>
+        <v>135322139</v>
       </c>
       <c r="B40" t="n">
         <v>79992</v>
@@ -4859,10 +4854,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617729</v>
+        <v>617634</v>
       </c>
       <c r="R40" t="n">
-        <v>7316047</v>
+        <v>7316176</v>
       </c>
       <c r="S40" t="n">
         <v>6</v>
@@ -4935,7 +4930,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135322139</v>
+        <v>135322945</v>
       </c>
       <c r="B41" t="n">
         <v>79992</v>
@@ -4966,17 +4961,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>617634</v>
+        <v>617566</v>
       </c>
       <c r="R41" t="n">
-        <v>7316176</v>
+        <v>7316256</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5005,7 +5000,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5015,7 +5010,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5030,12 +5025,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5046,7 +5041,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135322945</v>
+        <v>135325797</v>
       </c>
       <c r="B42" t="n">
         <v>79992</v>
@@ -5077,17 +5072,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>617566</v>
+        <v>617722</v>
       </c>
       <c r="R42" t="n">
-        <v>7316256</v>
+        <v>7316104</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5116,7 +5111,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5126,7 +5121,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5141,12 +5136,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5157,7 +5152,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135325797</v>
+        <v>135325811</v>
       </c>
       <c r="B43" t="n">
         <v>79992</v>
@@ -5192,13 +5187,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>617722</v>
+        <v>617596</v>
       </c>
       <c r="R43" t="n">
-        <v>7316104</v>
+        <v>7316363</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5227,7 +5222,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5237,7 +5232,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5268,7 +5263,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135325811</v>
+        <v>135325821</v>
       </c>
       <c r="B44" t="n">
         <v>79992</v>
@@ -5303,13 +5298,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>617596</v>
+        <v>617586</v>
       </c>
       <c r="R44" t="n">
-        <v>7316363</v>
+        <v>7316239</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5338,7 +5333,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5348,7 +5343,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5379,7 +5374,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135325821</v>
+        <v>135325825</v>
       </c>
       <c r="B45" t="n">
         <v>79992</v>
@@ -5414,13 +5409,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>617586</v>
+        <v>617617</v>
       </c>
       <c r="R45" t="n">
-        <v>7316239</v>
+        <v>7316184</v>
       </c>
       <c r="S45" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5449,7 +5444,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5459,7 +5454,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5490,7 +5485,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135325825</v>
+        <v>135326163</v>
       </c>
       <c r="B46" t="n">
         <v>79992</v>
@@ -5521,17 +5516,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>617617</v>
+        <v>617613</v>
       </c>
       <c r="R46" t="n">
-        <v>7316184</v>
+        <v>7316170</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5560,7 +5555,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5570,27 +5565,28 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5601,7 +5597,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135326163</v>
+        <v>135336181</v>
       </c>
       <c r="B47" t="n">
         <v>79992</v>
@@ -5632,17 +5628,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>617613</v>
+        <v>617647</v>
       </c>
       <c r="R47" t="n">
-        <v>7316170</v>
+        <v>7316156</v>
       </c>
       <c r="S47" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5671,7 +5667,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5681,28 +5677,42 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Gammal tallrotvälta # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5713,10 +5723,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135336181</v>
+        <v>96019502</v>
       </c>
       <c r="B48" t="n">
-        <v>79992</v>
+        <v>78334</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5724,37 +5734,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Maskaure, Långmyran, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>617647</v>
+        <v>617477</v>
       </c>
       <c r="R48" t="n">
-        <v>7316156</v>
+        <v>7316220</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5778,22 +5788,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:52</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:52</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5804,83 +5804,72 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Gammal tallrotvälta # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>96019502</v>
+        <v>135326174</v>
       </c>
       <c r="B49" t="n">
-        <v>78334</v>
+        <v>57972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6487</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>617477</v>
+        <v>617512</v>
       </c>
       <c r="R49" t="n">
-        <v>7316220</v>
+        <v>7316190</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5904,19 +5893,34 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG49" t="b">
         <v>0</v>
@@ -5924,39 +5928,43 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135326174</v>
+        <v>135322941</v>
       </c>
       <c r="B50" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5965,27 +5973,24 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>617512</v>
+        <v>617391</v>
       </c>
       <c r="R50" t="n">
-        <v>7316190</v>
+        <v>7316296</v>
       </c>
       <c r="S50" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6014,7 +6019,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6024,19 +6029,14 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Födosök.</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="b">
         <v>0</v>
@@ -6044,12 +6044,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6060,7 +6060,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135322941</v>
+        <v>135326171</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -6089,24 +6089,27 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>617391</v>
+        <v>617392</v>
       </c>
       <c r="R51" t="n">
-        <v>7316296</v>
+        <v>7316308</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6135,7 +6138,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6145,7 +6148,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6160,12 +6168,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6176,56 +6184,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135326171</v>
+        <v>135322928</v>
       </c>
       <c r="B52" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>617392</v>
+        <v>617773</v>
       </c>
       <c r="R52" t="n">
-        <v>7316308</v>
+        <v>7316117</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6254,7 +6263,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6264,12 +6273,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6284,12 +6288,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6300,10 +6304,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135322928</v>
+        <v>135336171</v>
       </c>
       <c r="B53" t="n">
-        <v>57162</v>
+        <v>5201</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6311,43 +6315,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>617773</v>
+        <v>617710</v>
       </c>
       <c r="R53" t="n">
-        <v>7316117</v>
+        <v>7316168</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6379,7 +6374,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6389,7 +6384,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6400,16 +6395,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6420,7 +6430,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135336171</v>
+        <v>135336178</v>
       </c>
       <c r="B54" t="n">
         <v>5201</v>
@@ -6455,10 +6465,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>617710</v>
+        <v>617577</v>
       </c>
       <c r="R54" t="n">
-        <v>7316168</v>
+        <v>7316342</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6490,7 +6500,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6500,7 +6510,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6524,7 +6534,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Klen granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6546,48 +6556,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135336178</v>
+        <v>135336168</v>
       </c>
       <c r="B55" t="n">
-        <v>5201</v>
+        <v>41606</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>105930</v>
+        <v>215713</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>617577</v>
+        <v>617763</v>
       </c>
       <c r="R55" t="n">
-        <v>7316342</v>
+        <v>7316087</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6616,7 +6631,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6626,7 +6641,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6637,21 +6652,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Klen granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6672,53 +6672,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135336168</v>
+        <v>135326169</v>
       </c>
       <c r="B56" t="n">
-        <v>41606</v>
+        <v>98219</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>215713</v>
+        <v>219815</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Maskaure, Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>617763</v>
+        <v>617380</v>
       </c>
       <c r="R56" t="n">
-        <v>7316087</v>
+        <v>7316322</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6747,7 +6742,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6757,7 +6752,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6772,12 +6767,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6788,10 +6783,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135326169</v>
+        <v>135336172</v>
       </c>
       <c r="B57" t="n">
-        <v>98219</v>
+        <v>110023</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6799,37 +6794,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219815</v>
+        <v>220263</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Fjällskråp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Petasites frigidus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>617380</v>
+        <v>617694</v>
       </c>
       <c r="R57" t="n">
-        <v>7316322</v>
+        <v>7316205</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6858,7 +6853,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6868,7 +6863,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6883,12 +6878,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6899,10 +6894,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135336172</v>
+        <v>135336176</v>
       </c>
       <c r="B58" t="n">
-        <v>110023</v>
+        <v>99217</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6910,21 +6905,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220263</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällskråp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Petasites frigidus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6934,10 +6929,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>617694</v>
+        <v>617684</v>
       </c>
       <c r="R58" t="n">
-        <v>7316205</v>
+        <v>7316239</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6969,7 +6964,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6979,7 +6974,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7010,45 +7005,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135336176</v>
+        <v>135322932</v>
       </c>
       <c r="B59" t="n">
-        <v>99217</v>
+        <v>78382</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Maskaure, Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>617684</v>
+        <v>617752</v>
       </c>
       <c r="R59" t="n">
-        <v>7316239</v>
+        <v>7316138</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7080,7 +7075,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7090,7 +7085,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7105,12 +7100,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7121,7 +7116,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135322932</v>
+        <v>135326166</v>
       </c>
       <c r="B60" t="n">
         <v>78382</v>
@@ -7152,14 +7147,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>617752</v>
+        <v>617505</v>
       </c>
       <c r="R60" t="n">
-        <v>7316138</v>
+        <v>7316325</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7191,7 +7186,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7201,7 +7196,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7216,12 +7211,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7232,7 +7227,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135326166</v>
+        <v>135326173</v>
       </c>
       <c r="B61" t="n">
         <v>78382</v>
@@ -7267,10 +7262,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>617505</v>
+        <v>617462</v>
       </c>
       <c r="R61" t="n">
-        <v>7316325</v>
+        <v>7316207</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7302,7 +7297,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7312,7 +7307,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7343,10 +7338,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135326173</v>
+        <v>135322946</v>
       </c>
       <c r="B62" t="n">
-        <v>78382</v>
+        <v>79963</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7354,37 +7349,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228579</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>617462</v>
+        <v>617647</v>
       </c>
       <c r="R62" t="n">
-        <v>7316207</v>
+        <v>7316156</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7413,7 +7408,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7423,7 +7418,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7438,12 +7433,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7454,10 +7449,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135322946</v>
+        <v>135322948</v>
       </c>
       <c r="B63" t="n">
-        <v>79963</v>
+        <v>79396</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7465,21 +7460,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>260591</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7489,13 +7484,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>617647</v>
+        <v>617649</v>
       </c>
       <c r="R63" t="n">
         <v>7316156</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7524,7 +7519,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7534,7 +7529,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Med gula soral</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7565,7 +7565,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135322948</v>
+        <v>135326162</v>
       </c>
       <c r="B64" t="n">
         <v>79396</v>
@@ -7596,17 +7596,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>617649</v>
+        <v>617639</v>
       </c>
       <c r="R64" t="n">
-        <v>7316156</v>
+        <v>7316143</v>
       </c>
       <c r="S64" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7645,12 +7645,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Med gula soral</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7665,12 +7660,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7681,48 +7676,43 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135326162</v>
+        <v>135322935</v>
       </c>
       <c r="B65" t="n">
-        <v>79396</v>
+        <v>80267</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
+        <v>266179</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lecidea subhumida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Vain.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>617639</v>
+        <v>617720</v>
       </c>
       <c r="R65" t="n">
-        <v>7316143</v>
+        <v>7316234</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7751,7 +7741,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7761,7 +7751,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7776,12 +7766,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7792,7 +7782,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135322935</v>
+        <v>135322939</v>
       </c>
       <c r="B66" t="n">
         <v>80267</v>
@@ -7822,13 +7812,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>617720</v>
+        <v>617550</v>
       </c>
       <c r="R66" t="n">
-        <v>7316234</v>
+        <v>7316331</v>
       </c>
       <c r="S66" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7857,7 +7847,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7867,7 +7857,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7891,112 +7881,6 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>135322939</v>
-      </c>
-      <c r="B67" t="n">
-        <v>80267</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>266179</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Lecidea subhumida</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Vain.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Maskaure Långmyran, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>617550</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7316331</v>
-      </c>
-      <c r="S67" t="n">
-        <v>9</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2733,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96019501</v>
+        <v>135336173</v>
       </c>
       <c r="B21" t="n">
-        <v>92333</v>
+        <v>96389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2744,37 +2744,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4217</v>
+        <v>2664</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Klomossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dichelyma falcatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Myrin</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617402</v>
+        <v>617689</v>
       </c>
       <c r="R21" t="n">
-        <v>7316257</v>
+        <v>7316215</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2798,17 +2802,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2817,50 +2826,55 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96019503</v>
+        <v>96019501</v>
       </c>
       <c r="B22" t="n">
-        <v>89156</v>
+        <v>92333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>4217</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2884,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617439</v>
+        <v>617402</v>
       </c>
       <c r="R22" t="n">
-        <v>7316241</v>
+        <v>7316257</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,6 +2920,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2932,48 +2951,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135322930</v>
+        <v>96019503</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>89156</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617763</v>
+        <v>617439</v>
       </c>
       <c r="R23" t="n">
-        <v>7316118</v>
+        <v>7316241</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2997,22 +3016,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,23 +3036,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135322933</v>
+        <v>135322930</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3078,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617745</v>
+        <v>617763</v>
       </c>
       <c r="R24" t="n">
-        <v>7316136</v>
+        <v>7316118</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,7 +3118,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3123,7 +3128,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,7 +3159,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135325800</v>
+        <v>135322933</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3185,17 +3190,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>617692</v>
+        <v>617745</v>
       </c>
       <c r="R25" t="n">
-        <v>7316206</v>
+        <v>7316136</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3224,7 +3229,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3234,7 +3239,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3249,12 +3254,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3265,7 +3270,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135325808</v>
+        <v>135325800</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3300,13 +3305,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>617658</v>
+        <v>617692</v>
       </c>
       <c r="R26" t="n">
-        <v>7316334</v>
+        <v>7316206</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3335,7 +3340,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3345,7 +3350,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3376,7 +3381,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135325820</v>
+        <v>135325808</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3411,13 +3416,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>617505</v>
+        <v>617658</v>
       </c>
       <c r="R27" t="n">
-        <v>7316297</v>
+        <v>7316334</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3446,7 +3451,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3456,7 +3461,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3487,32 +3492,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135325824</v>
+        <v>135325820</v>
       </c>
       <c r="B28" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3522,13 +3527,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>617617</v>
+        <v>617505</v>
       </c>
       <c r="R28" t="n">
-        <v>7316184</v>
+        <v>7316297</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3557,7 +3562,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3567,7 +3572,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3598,7 +3603,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135326164</v>
+        <v>135325824</v>
       </c>
       <c r="B29" t="n">
         <v>78776</v>
@@ -3629,14 +3634,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>617552</v>
+        <v>617617</v>
       </c>
       <c r="R29" t="n">
-        <v>7316225</v>
+        <v>7316184</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3668,7 +3673,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3678,7 +3683,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3693,12 +3698,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3709,10 +3714,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135322133</v>
+        <v>135326164</v>
       </c>
       <c r="B30" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,34 +3725,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617704</v>
+        <v>617552</v>
       </c>
       <c r="R30" t="n">
-        <v>7316223</v>
+        <v>7316225</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3779,7 +3784,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3789,7 +3794,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3804,12 +3809,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3820,7 +3825,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135322927</v>
+        <v>135322133</v>
       </c>
       <c r="B31" t="n">
         <v>83358</v>
@@ -3851,14 +3856,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617778</v>
+        <v>617704</v>
       </c>
       <c r="R31" t="n">
-        <v>7316112</v>
+        <v>7316223</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3890,7 +3895,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3900,7 +3905,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,12 +3920,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3931,7 +3936,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135322940</v>
+        <v>135322927</v>
       </c>
       <c r="B32" t="n">
         <v>83358</v>
@@ -3966,13 +3971,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>617520</v>
+        <v>617778</v>
       </c>
       <c r="R32" t="n">
-        <v>7316320</v>
+        <v>7316112</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4001,7 +4006,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4011,7 +4016,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,7 +4047,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135325798</v>
+        <v>135322940</v>
       </c>
       <c r="B33" t="n">
         <v>83358</v>
@@ -4073,17 +4078,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>617722</v>
+        <v>617520</v>
       </c>
       <c r="R33" t="n">
-        <v>7316104</v>
+        <v>7316320</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4112,7 +4117,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4122,7 +4127,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,12 +4142,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4153,7 +4158,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135325799</v>
+        <v>135325798</v>
       </c>
       <c r="B34" t="n">
         <v>83358</v>
@@ -4188,13 +4193,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>617701</v>
+        <v>617722</v>
       </c>
       <c r="R34" t="n">
-        <v>7316164</v>
+        <v>7316104</v>
       </c>
       <c r="S34" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4223,7 +4228,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4233,7 +4238,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4264,7 +4269,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135325801</v>
+        <v>135325799</v>
       </c>
       <c r="B35" t="n">
         <v>83358</v>
@@ -4299,13 +4304,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617709</v>
+        <v>617701</v>
       </c>
       <c r="R35" t="n">
-        <v>7316204</v>
+        <v>7316164</v>
       </c>
       <c r="S35" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4334,7 +4339,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4344,7 +4349,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4375,7 +4380,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135325805</v>
+        <v>135325801</v>
       </c>
       <c r="B36" t="n">
         <v>83358</v>
@@ -4410,13 +4415,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617678</v>
+        <v>617709</v>
       </c>
       <c r="R36" t="n">
-        <v>7316280</v>
+        <v>7316204</v>
       </c>
       <c r="S36" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4445,7 +4450,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4455,7 +4460,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4486,7 +4491,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135325813</v>
+        <v>135325805</v>
       </c>
       <c r="B37" t="n">
         <v>83358</v>
@@ -4521,13 +4526,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>617583</v>
+        <v>617678</v>
       </c>
       <c r="R37" t="n">
-        <v>7316339</v>
+        <v>7316280</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4556,7 +4561,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4566,7 +4571,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4597,10 +4602,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135322137</v>
+        <v>135325813</v>
       </c>
       <c r="B38" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4608,37 +4613,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>617622</v>
+        <v>617583</v>
       </c>
       <c r="R38" t="n">
-        <v>7316280</v>
+        <v>7316339</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4667,7 +4672,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4677,7 +4682,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4692,12 +4697,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4708,7 +4713,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135322138</v>
+        <v>135322137</v>
       </c>
       <c r="B39" t="n">
         <v>79992</v>
@@ -4743,10 +4748,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617729</v>
+        <v>617622</v>
       </c>
       <c r="R39" t="n">
-        <v>7316047</v>
+        <v>7316280</v>
       </c>
       <c r="S39" t="n">
         <v>6</v>
@@ -4778,7 +4783,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4788,7 +4793,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4819,7 +4824,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135322139</v>
+        <v>135322138</v>
       </c>
       <c r="B40" t="n">
         <v>79992</v>
@@ -4854,10 +4859,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617634</v>
+        <v>617729</v>
       </c>
       <c r="R40" t="n">
-        <v>7316176</v>
+        <v>7316047</v>
       </c>
       <c r="S40" t="n">
         <v>6</v>
@@ -4930,7 +4935,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135322945</v>
+        <v>135322139</v>
       </c>
       <c r="B41" t="n">
         <v>79992</v>
@@ -4961,17 +4966,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>617566</v>
+        <v>617634</v>
       </c>
       <c r="R41" t="n">
-        <v>7316256</v>
+        <v>7316176</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5000,7 +5005,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5010,7 +5015,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5025,12 +5030,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5041,7 +5046,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135325797</v>
+        <v>135322945</v>
       </c>
       <c r="B42" t="n">
         <v>79992</v>
@@ -5072,17 +5077,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>617722</v>
+        <v>617566</v>
       </c>
       <c r="R42" t="n">
-        <v>7316104</v>
+        <v>7316256</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5111,7 +5116,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5121,7 +5126,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5136,12 +5141,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5152,7 +5157,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135325811</v>
+        <v>135325797</v>
       </c>
       <c r="B43" t="n">
         <v>79992</v>
@@ -5187,13 +5192,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>617596</v>
+        <v>617722</v>
       </c>
       <c r="R43" t="n">
-        <v>7316363</v>
+        <v>7316104</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5222,7 +5227,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5232,7 +5237,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5263,7 +5268,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135325821</v>
+        <v>135325811</v>
       </c>
       <c r="B44" t="n">
         <v>79992</v>
@@ -5298,13 +5303,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>617586</v>
+        <v>617596</v>
       </c>
       <c r="R44" t="n">
-        <v>7316239</v>
+        <v>7316363</v>
       </c>
       <c r="S44" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5333,7 +5338,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5343,7 +5348,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5374,7 +5379,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135325825</v>
+        <v>135325821</v>
       </c>
       <c r="B45" t="n">
         <v>79992</v>
@@ -5409,13 +5414,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>617617</v>
+        <v>617586</v>
       </c>
       <c r="R45" t="n">
-        <v>7316184</v>
+        <v>7316239</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5444,7 +5449,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5454,7 +5459,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5485,7 +5490,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135326163</v>
+        <v>135325825</v>
       </c>
       <c r="B46" t="n">
         <v>79992</v>
@@ -5516,17 +5521,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>617613</v>
+        <v>617617</v>
       </c>
       <c r="R46" t="n">
-        <v>7316170</v>
+        <v>7316184</v>
       </c>
       <c r="S46" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5555,7 +5560,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5565,28 +5570,27 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5597,7 +5601,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135336181</v>
+        <v>135326163</v>
       </c>
       <c r="B47" t="n">
         <v>79992</v>
@@ -5628,17 +5632,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Maskaure, Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>617647</v>
+        <v>617613</v>
       </c>
       <c r="R47" t="n">
-        <v>7316156</v>
+        <v>7316170</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5667,7 +5671,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5677,42 +5681,28 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Gammal tallrotvälta # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5723,10 +5713,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>96019502</v>
+        <v>135336181</v>
       </c>
       <c r="B48" t="n">
-        <v>78334</v>
+        <v>79992</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5734,37 +5724,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>617477</v>
+        <v>617647</v>
       </c>
       <c r="R48" t="n">
-        <v>7316220</v>
+        <v>7316156</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5788,12 +5778,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5804,72 +5804,83 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Gammal tallrotvälta # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135326174</v>
+        <v>96019502</v>
       </c>
       <c r="B49" t="n">
-        <v>57972</v>
+        <v>78334</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>617512</v>
+        <v>617477</v>
       </c>
       <c r="R49" t="n">
-        <v>7316190</v>
+        <v>7316220</v>
       </c>
       <c r="S49" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5893,34 +5904,19 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Födosök.</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="b">
         <v>0</v>
@@ -5928,43 +5924,39 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135322941</v>
+        <v>135326174</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5973,24 +5965,27 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>617391</v>
+        <v>617512</v>
       </c>
       <c r="R50" t="n">
-        <v>7316296</v>
+        <v>7316190</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6019,7 +6014,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6029,14 +6024,19 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG50" t="b">
         <v>0</v>
@@ -6044,12 +6044,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6060,7 +6060,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135326171</v>
+        <v>135322941</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -6089,27 +6089,24 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>617392</v>
+        <v>617391</v>
       </c>
       <c r="R51" t="n">
-        <v>7316308</v>
+        <v>7316296</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6138,7 +6135,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6148,12 +6145,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6168,12 +6160,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6184,57 +6176,56 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135322928</v>
+        <v>135326171</v>
       </c>
       <c r="B52" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>617773</v>
+        <v>617392</v>
       </c>
       <c r="R52" t="n">
-        <v>7316117</v>
+        <v>7316308</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6263,7 +6254,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6273,7 +6264,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6288,12 +6284,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6304,10 +6300,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135336171</v>
+        <v>135322928</v>
       </c>
       <c r="B53" t="n">
-        <v>5201</v>
+        <v>57162</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6315,34 +6311,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Maskaure, Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>617710</v>
+        <v>617773</v>
       </c>
       <c r="R53" t="n">
-        <v>7316168</v>
+        <v>7316117</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6374,7 +6379,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6384,7 +6389,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6395,31 +6400,16 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6430,7 +6420,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135336178</v>
+        <v>135336171</v>
       </c>
       <c r="B54" t="n">
         <v>5201</v>
@@ -6465,10 +6455,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>617577</v>
+        <v>617710</v>
       </c>
       <c r="R54" t="n">
-        <v>7316342</v>
+        <v>7316168</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6500,7 +6490,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6510,7 +6500,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6534,7 +6524,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Klen granlåga # Picea abies</t>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6545,7 +6535,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6556,53 +6546,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135336168</v>
+        <v>135336178</v>
       </c>
       <c r="B55" t="n">
-        <v>41606</v>
+        <v>5201</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>215713</v>
+        <v>105930</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>617763</v>
+        <v>617577</v>
       </c>
       <c r="R55" t="n">
-        <v>7316087</v>
+        <v>7316342</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6631,7 +6616,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6641,7 +6626,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6652,6 +6637,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Klen granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6672,48 +6672,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135326169</v>
+        <v>135336168</v>
       </c>
       <c r="B56" t="n">
-        <v>98219</v>
+        <v>41606</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219815</v>
+        <v>215713</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>617380</v>
+        <v>617763</v>
       </c>
       <c r="R56" t="n">
-        <v>7316322</v>
+        <v>7316087</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6742,7 +6747,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6752,7 +6757,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6767,12 +6772,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6783,10 +6788,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135336172</v>
+        <v>135326169</v>
       </c>
       <c r="B57" t="n">
-        <v>110023</v>
+        <v>98219</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6794,37 +6799,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220263</v>
+        <v>219815</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällskråp</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Petasites frigidus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Maskaure, Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>617694</v>
+        <v>617380</v>
       </c>
       <c r="R57" t="n">
-        <v>7316205</v>
+        <v>7316322</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6853,7 +6858,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6863,7 +6868,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6878,12 +6883,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6894,10 +6899,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135336176</v>
+        <v>135336172</v>
       </c>
       <c r="B58" t="n">
-        <v>99217</v>
+        <v>110023</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6905,21 +6910,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>220263</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fjällskråp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Petasites frigidus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6929,10 +6934,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>617684</v>
+        <v>617694</v>
       </c>
       <c r="R58" t="n">
-        <v>7316239</v>
+        <v>7316205</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6964,7 +6969,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6974,7 +6979,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6994,7 +6999,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7005,45 +7010,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135322932</v>
+        <v>135336176</v>
       </c>
       <c r="B59" t="n">
-        <v>78382</v>
+        <v>99217</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure, Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>617752</v>
+        <v>617684</v>
       </c>
       <c r="R59" t="n">
-        <v>7316138</v>
+        <v>7316239</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7075,7 +7080,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7085,7 +7090,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7100,12 +7105,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7116,7 +7121,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135326166</v>
+        <v>135322932</v>
       </c>
       <c r="B60" t="n">
         <v>78382</v>
@@ -7147,14 +7152,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>617505</v>
+        <v>617752</v>
       </c>
       <c r="R60" t="n">
-        <v>7316325</v>
+        <v>7316138</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7186,7 +7191,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7196,7 +7201,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7211,12 +7216,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7227,7 +7232,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135326173</v>
+        <v>135326166</v>
       </c>
       <c r="B61" t="n">
         <v>78382</v>
@@ -7262,10 +7267,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>617462</v>
+        <v>617505</v>
       </c>
       <c r="R61" t="n">
-        <v>7316207</v>
+        <v>7316325</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7297,7 +7302,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7307,7 +7312,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7338,10 +7343,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135322946</v>
+        <v>135326173</v>
       </c>
       <c r="B62" t="n">
-        <v>79963</v>
+        <v>78382</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7349,37 +7354,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>617647</v>
+        <v>617462</v>
       </c>
       <c r="R62" t="n">
-        <v>7316156</v>
+        <v>7316207</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7408,7 +7413,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7418,7 +7423,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7433,12 +7438,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7449,10 +7454,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135322948</v>
+        <v>135322946</v>
       </c>
       <c r="B63" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7460,21 +7465,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7484,13 +7489,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>617649</v>
+        <v>617647</v>
       </c>
       <c r="R63" t="n">
         <v>7316156</v>
       </c>
       <c r="S63" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7519,7 +7524,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7529,12 +7534,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Med gula soral</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7565,7 +7565,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135326162</v>
+        <v>135322948</v>
       </c>
       <c r="B64" t="n">
         <v>79396</v>
@@ -7596,17 +7596,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>617639</v>
+        <v>617649</v>
       </c>
       <c r="R64" t="n">
-        <v>7316143</v>
+        <v>7316156</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7645,7 +7645,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Med gula soral</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7660,12 +7665,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7676,43 +7681,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135322935</v>
+        <v>135326162</v>
       </c>
       <c r="B65" t="n">
-        <v>80267</v>
+        <v>79396</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>266179</v>
+        <v>260591</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran, Pi lm</t>
+          <t>Maskaure Långmyran SV, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>617720</v>
+        <v>617639</v>
       </c>
       <c r="R65" t="n">
-        <v>7316234</v>
+        <v>7316143</v>
       </c>
       <c r="S65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7741,7 +7751,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7751,7 +7761,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7766,12 +7776,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7782,7 +7792,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135322939</v>
+        <v>135322935</v>
       </c>
       <c r="B66" t="n">
         <v>80267</v>
@@ -7812,13 +7822,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>617550</v>
+        <v>617720</v>
       </c>
       <c r="R66" t="n">
-        <v>7316331</v>
+        <v>7316234</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7847,7 +7857,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7857,7 +7867,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7881,6 +7891,112 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135322939</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80267</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>617550</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7316331</v>
+      </c>
+      <c r="S67" t="n">
+        <v>9</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322135</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322136</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322938</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322942</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322944</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325822</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019469</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019458</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1643,6 +1688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322936</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1754,6 +1804,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325803</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1851,6 +1906,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019482</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1948,6 +2008,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019492</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2059,6 +2124,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325809</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325817</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2279,6 +2354,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322937</t>
         </is>
       </c>
     </row>
@@ -2411,6 +2491,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336170</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2508,6 +2593,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019471</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2619,6 +2709,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325814</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2728,6 +2823,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325815</t>
         </is>
       </c>
     </row>
@@ -2846,6 +2946,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336173</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2948,6 +3053,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019501</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3045,6 +3155,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019503</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3156,6 +3271,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322930</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3267,6 +3387,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322933</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3378,6 +3503,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325800</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3489,6 +3619,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325808</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3600,6 +3735,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325820</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3711,6 +3851,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325824</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3822,6 +3967,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326164</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3933,6 +4083,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322133</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4044,6 +4199,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322927</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4155,6 +4315,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322940</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4266,6 +4431,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325798</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4377,6 +4547,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325799</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4488,6 +4663,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325801</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4599,6 +4779,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325805</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4710,6 +4895,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325813</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4821,6 +5011,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322137</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4932,6 +5127,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322138</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5043,6 +5243,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322139</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5154,6 +5359,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322945</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5265,6 +5475,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325797</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5376,6 +5591,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325811</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5487,6 +5707,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325821</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5598,6 +5823,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325825</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5710,6 +5940,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326163</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5836,6 +6071,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336181</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5933,6 +6173,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019502</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6057,6 +6302,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326174</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6173,6 +6423,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322941</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6297,6 +6552,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326171</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6417,6 +6677,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322928</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6543,6 +6808,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336171</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6669,6 +6939,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336178</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6785,6 +7060,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336168</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6896,6 +7176,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326169</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7007,6 +7292,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336172</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7118,6 +7408,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336176</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7229,6 +7524,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322932</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7340,6 +7640,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326166</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7451,6 +7756,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326173</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7562,6 +7872,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322946</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7678,6 +7993,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322948</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7789,6 +8109,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326162</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7895,6 +8220,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322935</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8001,8 +8331,81 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322939</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135322135</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135322136</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135322938</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135322942</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135322944</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135325822</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135322936</v>
       </c>
       <c r="B10" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>135325803</v>
       </c>
       <c r="B11" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>135325809</v>
       </c>
       <c r="B14" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>135325817</v>
       </c>
       <c r="B15" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135322937</v>
       </c>
       <c r="B16" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135336170</v>
       </c>
       <c r="B17" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>135325814</v>
       </c>
       <c r="B19" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135325815</v>
       </c>
       <c r="B20" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>135336173</v>
       </c>
       <c r="B21" t="n">
-        <v>96389</v>
+        <v>96433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>135322930</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>135322933</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>135325800</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>135325808</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>135325820</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>135325824</v>
       </c>
       <c r="B29" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>135326164</v>
       </c>
       <c r="B30" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>135322133</v>
       </c>
       <c r="B31" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>135322927</v>
       </c>
       <c r="B32" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135322940</v>
       </c>
       <c r="B33" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>135325798</v>
       </c>
       <c r="B34" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>135325799</v>
       </c>
       <c r="B35" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>135325801</v>
       </c>
       <c r="B36" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>135325805</v>
       </c>
       <c r="B37" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>135325813</v>
       </c>
       <c r="B38" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>135322137</v>
       </c>
       <c r="B39" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>135322138</v>
       </c>
       <c r="B40" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>135322139</v>
       </c>
       <c r="B41" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>135322945</v>
       </c>
       <c r="B42" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>135325797</v>
       </c>
       <c r="B43" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>135325811</v>
       </c>
       <c r="B44" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135325821</v>
       </c>
       <c r="B45" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>135325825</v>
       </c>
       <c r="B46" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>135326163</v>
       </c>
       <c r="B47" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>135336181</v>
       </c>
       <c r="B48" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>135326174</v>
       </c>
       <c r="B50" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>135322941</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>135326171</v>
       </c>
       <c r="B52" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>135322928</v>
       </c>
       <c r="B53" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>135336168</v>
       </c>
       <c r="B56" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>135326169</v>
       </c>
       <c r="B57" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>135336172</v>
       </c>
       <c r="B58" t="n">
-        <v>110023</v>
+        <v>110079</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>135336176</v>
       </c>
       <c r="B59" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>135322932</v>
       </c>
       <c r="B60" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>135326166</v>
       </c>
       <c r="B61" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>135326173</v>
       </c>
       <c r="B62" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>135322946</v>
       </c>
       <c r="B63" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>135322948</v>
       </c>
       <c r="B64" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>135326162</v>
       </c>
       <c r="B65" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>135322935</v>
       </c>
       <c r="B66" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>135322939</v>
       </c>
       <c r="B67" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135322135</v>
       </c>
       <c r="B2" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135322136</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135322938</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135322942</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135322944</v>
       </c>
       <c r="B6" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135325822</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135322936</v>
       </c>
       <c r="B10" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>135325803</v>
       </c>
       <c r="B11" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>135325809</v>
       </c>
       <c r="B14" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>135325817</v>
       </c>
       <c r="B15" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135322937</v>
       </c>
       <c r="B16" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135336170</v>
       </c>
       <c r="B17" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2604,7 +2604,7 @@
         <v>135325814</v>
       </c>
       <c r="B19" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135325815</v>
       </c>
       <c r="B20" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>135336173</v>
       </c>
       <c r="B21" t="n">
-        <v>96433</v>
+        <v>96460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3166,7 +3166,7 @@
         <v>135322930</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>135322933</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>135325800</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>135325808</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>135325820</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>135325824</v>
       </c>
       <c r="B29" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>135326164</v>
       </c>
       <c r="B30" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>135322133</v>
       </c>
       <c r="B31" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>135322927</v>
       </c>
       <c r="B32" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135322940</v>
       </c>
       <c r="B33" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>135325798</v>
       </c>
       <c r="B34" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>135325799</v>
       </c>
       <c r="B35" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>135325801</v>
       </c>
       <c r="B36" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>135325805</v>
       </c>
       <c r="B37" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>135325813</v>
       </c>
       <c r="B38" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>135322137</v>
       </c>
       <c r="B39" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>135322138</v>
       </c>
       <c r="B40" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>135322139</v>
       </c>
       <c r="B41" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>135322945</v>
       </c>
       <c r="B42" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>135325797</v>
       </c>
       <c r="B43" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>135325811</v>
       </c>
       <c r="B44" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135325821</v>
       </c>
       <c r="B45" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>135325825</v>
       </c>
       <c r="B46" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>135326163</v>
       </c>
       <c r="B47" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>135336181</v>
       </c>
       <c r="B48" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -7071,7 +7071,7 @@
         <v>135326169</v>
       </c>
       <c r="B57" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>135336172</v>
       </c>
       <c r="B58" t="n">
-        <v>110079</v>
+        <v>110106</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7303,7 +7303,7 @@
         <v>135336176</v>
       </c>
       <c r="B59" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7419,7 +7419,7 @@
         <v>135322932</v>
       </c>
       <c r="B60" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>135326166</v>
       </c>
       <c r="B61" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>135326173</v>
       </c>
       <c r="B62" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>135322946</v>
       </c>
       <c r="B63" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>135322948</v>
       </c>
       <c r="B64" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>135326162</v>
       </c>
       <c r="B65" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>135322935</v>
       </c>
       <c r="B66" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>135322939</v>
       </c>
       <c r="B67" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96019469</v>
+        <v>135322135</v>
       </c>
       <c r="B2" t="n">
-        <v>79406</v>
+        <v>79107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617402</v>
+        <v>617665</v>
       </c>
       <c r="R2" t="n">
-        <v>7316257</v>
+        <v>7316240</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +775,31 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019469</t>
+          <t>https://artportalen.se/Sighting/135322135</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96019458</v>
+        <v>135322136</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>79107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617434</v>
+        <v>617641</v>
       </c>
       <c r="R3" t="n">
-        <v>7316243</v>
+        <v>7316212</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,65 +891,69 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019458</t>
+          <t>https://artportalen.se/Sighting/135322136</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96019482</v>
+        <v>135322938</v>
       </c>
       <c r="B4" t="n">
-        <v>91923</v>
+        <v>79107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617446</v>
+        <v>617598</v>
       </c>
       <c r="R4" t="n">
-        <v>7316215</v>
+        <v>7316361</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +977,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +1007,31 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019482</t>
+          <t>https://artportalen.se/Sighting/135322938</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96019492</v>
+        <v>135322942</v>
       </c>
       <c r="B5" t="n">
-        <v>83173</v>
+        <v>79107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,37 +1039,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617402</v>
+        <v>617372</v>
       </c>
       <c r="R5" t="n">
-        <v>7316257</v>
+        <v>7316267</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1093,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,65 +1123,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019492</t>
+          <t>https://artportalen.se/Sighting/135322942</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96019471</v>
+        <v>135322944</v>
       </c>
       <c r="B6" t="n">
-        <v>92283</v>
+        <v>79107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2063</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>617488</v>
+        <v>617566</v>
       </c>
       <c r="R6" t="n">
-        <v>7316243</v>
+        <v>7316256</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1209,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,65 +1239,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019471</t>
+          <t>https://artportalen.se/Sighting/135322944</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96019501</v>
+        <v>135325822</v>
       </c>
       <c r="B7" t="n">
-        <v>92333</v>
+        <v>79107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>617402</v>
+        <v>617605</v>
       </c>
       <c r="R7" t="n">
-        <v>7316257</v>
+        <v>7316186</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,17 +1325,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,27 +1355,31 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019501</t>
+          <t>https://artportalen.se/Sighting/135325822</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96019503</v>
+        <v>96019469</v>
       </c>
       <c r="B8" t="n">
-        <v>89156</v>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4412</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>617439</v>
+        <v>617402</v>
       </c>
       <c r="R8" t="n">
-        <v>7316241</v>
+        <v>7316257</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,16 +1472,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019503</t>
+          <t>https://artportalen.se/Sighting/96019469</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96019502</v>
+        <v>96019458</v>
       </c>
       <c r="B9" t="n">
-        <v>78334</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1489,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>617477</v>
+        <v>617434</v>
       </c>
       <c r="R9" t="n">
-        <v>7316220</v>
+        <v>7316243</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,7 +1574,6766 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/96019458</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135322936</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>617703</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7316246</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322936</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135325803</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>617698</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7316266</v>
+      </c>
+      <c r="S11" t="n">
+        <v>27</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325803</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96019482</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>617446</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7316215</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Julian Klein</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019482</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>96019492</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>617402</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7316257</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Julian Klein</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019492</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135325809</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83292</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>617658</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7316336</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325809</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135325817</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83292</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>617421</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7316321</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325817</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135322937</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83433</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>617671</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7316275</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322937</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135336170</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83433</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Maskaure, Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>617752</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7316113</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>På barken av en björkstubbe # Betula</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336170</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>96019471</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92283</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>617488</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7316243</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Julian Klein</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019471</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135325814</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92394</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>617583</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7316339</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325814</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135325815</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>617465</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7316316</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325815</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135336173</v>
+      </c>
+      <c r="B21" t="n">
+        <v>96465</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2664</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Klomossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dichelyma falcatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hedw.) Myrin</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Maskaure, Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>617689</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7316215</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336173</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>96019501</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92333</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>617402</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7316257</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Julian Klein</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019501</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>96019503</v>
+      </c>
+      <c r="B23" t="n">
+        <v>89156</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>617439</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7316241</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Julian Klein</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019503</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135322930</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>617763</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7316118</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322930</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135322933</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>617745</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7316136</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322933</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135325800</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>617692</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7316206</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325800</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135325808</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>617658</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7316334</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325808</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135325820</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>617505</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7316297</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325820</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135325824</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>617617</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7316184</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325824</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135326164</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>617552</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7316225</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326164</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135322133</v>
+      </c>
+      <c r="B31" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>617704</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7316223</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322133</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135322927</v>
+      </c>
+      <c r="B32" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>617778</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7316112</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322927</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135322940</v>
+      </c>
+      <c r="B33" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>617520</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7316320</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322940</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135325798</v>
+      </c>
+      <c r="B34" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>617722</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7316104</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325798</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135325799</v>
+      </c>
+      <c r="B35" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>617701</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7316164</v>
+      </c>
+      <c r="S35" t="n">
+        <v>54</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325799</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135325801</v>
+      </c>
+      <c r="B36" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>617709</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7316204</v>
+      </c>
+      <c r="S36" t="n">
+        <v>42</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325801</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135325805</v>
+      </c>
+      <c r="B37" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>617678</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7316280</v>
+      </c>
+      <c r="S37" t="n">
+        <v>43</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325805</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135325813</v>
+      </c>
+      <c r="B38" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>617583</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7316339</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325813</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135322137</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>617622</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7316280</v>
+      </c>
+      <c r="S39" t="n">
+        <v>6</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322137</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135322138</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>617729</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7316047</v>
+      </c>
+      <c r="S40" t="n">
+        <v>6</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322138</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135322139</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>617634</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7316176</v>
+      </c>
+      <c r="S41" t="n">
+        <v>6</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322139</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135322945</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>617566</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7316256</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322945</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135325797</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>617722</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7316104</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325797</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135325811</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>617596</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7316363</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325811</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135325821</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>617586</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7316239</v>
+      </c>
+      <c r="S45" t="n">
+        <v>77</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325821</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135325825</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>617617</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7316184</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325825</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135326163</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>617613</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7316170</v>
+      </c>
+      <c r="S47" t="n">
+        <v>24</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326163</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135336181</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Maskaure, Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>617647</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7316156</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Gammal tallrotvälta # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336181</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>96019502</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>617477</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7316220</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Julian Klein</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/96019502</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135326174</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>617512</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7316190</v>
+      </c>
+      <c r="S50" t="n">
+        <v>26</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Födosök.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326174</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135322941</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>617391</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7316296</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322941</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135326171</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>617392</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7316308</v>
+      </c>
+      <c r="S52" t="n">
+        <v>11</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326171</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135322928</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>617773</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7316117</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322928</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135336171</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Maskaure, Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>617710</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7316168</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336171</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135336178</v>
+      </c>
+      <c r="B55" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Maskaure, Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>617577</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7316342</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Klen granlåga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336178</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135336168</v>
+      </c>
+      <c r="B56" t="n">
+        <v>41610</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>215713</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Grå blåbärsfältmätare</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Entephria caesiata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Maskaure, Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>617763</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7316087</v>
+      </c>
+      <c r="S56" t="n">
+        <v>7</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336168</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135326169</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98295</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>617380</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7316322</v>
+      </c>
+      <c r="S57" t="n">
+        <v>6</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326169</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135336172</v>
+      </c>
+      <c r="B58" t="n">
+        <v>110111</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220263</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Fjällskråp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Petasites frigidus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Fr.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Maskaure, Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>617694</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7316205</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336172</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135336176</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Maskaure, Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>617684</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7316239</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336176</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135322932</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78450</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>617752</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7316138</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322932</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135326166</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78450</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>617505</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7316325</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326166</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135326173</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78450</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>617462</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7316207</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326173</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135322946</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>617647</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7316156</v>
+      </c>
+      <c r="S63" t="n">
+        <v>7</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322946</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135322948</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>617649</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7316156</v>
+      </c>
+      <c r="S64" t="n">
+        <v>14</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Med gula soral</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322948</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135326162</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>617639</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7316143</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326162</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135322935</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80335</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>617720</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7316234</v>
+      </c>
+      <c r="S66" t="n">
+        <v>6</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322935</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135322939</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80335</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>617550</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7316331</v>
+      </c>
+      <c r="S67" t="n">
+        <v>9</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322939</t>
         </is>
       </c>
     </row>
@@ -1509,6 +8347,64 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>135322936</v>
       </c>
       <c r="B10" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>135325803</v>
       </c>
       <c r="B11" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>135325814</v>
       </c>
       <c r="B19" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135325815</v>
       </c>
       <c r="B20" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>135336173</v>
       </c>
       <c r="B21" t="n">
-        <v>96465</v>
+        <v>96467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>135326169</v>
       </c>
       <c r="B57" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>135336172</v>
       </c>
       <c r="B58" t="n">
-        <v>110111</v>
+        <v>110113</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>135336176</v>
       </c>
       <c r="B59" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Långmyran SV, 6,8 ha artfynd.xlsx
@@ -2367,7 +2367,7 @@
         <v>135336170</v>
       </c>
       <c r="B17" t="n">
-        <v>83433</v>
+        <v>83435</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>135336173</v>
       </c>
       <c r="B21" t="n">
-        <v>96467</v>
+        <v>96484</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>135336181</v>
       </c>
       <c r="B48" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>135336171</v>
       </c>
       <c r="B54" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>135336178</v>
       </c>
       <c r="B55" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>135336168</v>
       </c>
       <c r="B56" t="n">
-        <v>41610</v>
+        <v>41612</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>135336172</v>
       </c>
       <c r="B58" t="n">
-        <v>110113</v>
+        <v>110136</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>135336176</v>
       </c>
       <c r="B59" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
